--- a/Codes/Compiled_rain/stormwatch_station_coverage_summary.xlsx
+++ b/Codes/Compiled_rain/stormwatch_station_coverage_summary.xlsx
@@ -488,12 +488,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2012-01-01 13:00</t>
+          <t>2012-01-02 00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2023-12-29 23:00</t>
+          <t>2023-12-30 10:00</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -509,7 +509,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2012-01-01 13:00 to 2023-12-29 23:00</t>
+          <t>2012-01-02 00:00 to 2023-12-30 10:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -526,12 +526,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2012-01-01 12:00</t>
+          <t>2012-01-01 23:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025-08-08 06:00</t>
+          <t>2025-08-08 17:00</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -550,12 +550,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2014-11-11 16:00 to 2014-11-20 05:00 (8.54 days) | 2017-02-07 07:00 to 2017-02-23 19:00 (16.50 days) | 2019-01-18 08:00 to 2019-01-31 08:00 (13.00 days) | 2020-11-13 03:00 to 2020-11-24 03:00 (11.00 days) | 2021-01-06 04:00 to 2021-01-16 04:00 (10.00 days) | 2021-02-24 16:00 to 2021-03-12 22:00 (16.25 days) | 2021-03-14 16:00 to 2021-04-16 06:00 (32.58 days) | 2022-08-16 06:00 to 2022-08-24 09:00 (8.12 days)</t>
+          <t>2014-11-12 03:00 to 2014-11-20 16:00 (8.54 days) | 2017-02-07 18:00 to 2017-02-24 06:00 (16.50 days) | 2019-01-18 19:00 to 2019-01-31 19:00 (13.00 days) | 2020-11-13 14:00 to 2020-11-24 14:00 (11.00 days) | 2021-01-06 15:00 to 2021-01-16 15:00 (10.00 days) | 2021-02-25 03:00 to 2021-03-13 09:00 (16.25 days) | 2021-03-15 03:00 to 2021-04-16 17:00 (32.58 days) | 2022-08-16 17:00 to 2022-08-24 20:00 (8.12 days)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2012-01-01 12:00 to 2014-11-11 16:00 | 2014-11-20 05:00 to 2017-02-07 07:00 | 2017-02-23 19:00 to 2019-01-18 08:00 | 2019-01-31 08:00 to 2020-11-13 03:00 | 2020-11-24 03:00 to 2021-01-06 04:00 | 2021-01-16 04:00 to 2021-02-24 16:00 | 2021-03-12 22:00 to 2021-03-14 16:00 | 2021-04-16 06:00 to 2022-08-16 06:00 | 2022-08-24 09:00 to 2025-08-08 06:00</t>
+          <t>2012-01-01 23:00 to 2014-11-12 03:00 | 2014-11-20 16:00 to 2017-02-07 18:00 | 2017-02-24 06:00 to 2019-01-18 19:00 | 2019-01-31 19:00 to 2020-11-13 14:00 | 2020-11-24 14:00 to 2021-01-06 15:00 | 2021-01-16 15:00 to 2021-02-25 03:00 | 2021-03-13 09:00 to 2021-03-15 03:00 | 2021-04-16 17:00 to 2022-08-16 17:00 | 2022-08-24 20:00 to 2025-08-08 17:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -572,12 +572,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2012-01-01 09:00</t>
+          <t>2012-01-01 20:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2025-08-08 01:00</t>
+          <t>2025-08-08 12:00</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -593,7 +593,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2012-01-01 09:00 to 2025-08-08 01:00</t>
+          <t>2012-01-01 20:00 to 2025-08-08 12:00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2012-01-01 15:00</t>
+          <t>2012-01-02 02:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2025-08-07 21:00</t>
+          <t>2025-08-08 08:00</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -634,12 +634,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2014-04-08 23:00 to 2014-06-06 04:00 (58.21 days) | 2020-12-28 16:00 to 2021-01-14 16:00 (17.00 days)</t>
+          <t>2014-04-09 10:00 to 2014-06-06 15:00 (58.21 days) | 2020-12-29 03:00 to 2021-01-15 03:00 (17.00 days)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2012-01-01 15:00 to 2014-04-08 23:00 | 2014-06-06 04:00 to 2020-12-28 16:00 | 2021-01-14 16:00 to 2025-08-07 21:00</t>
+          <t>2012-01-02 02:00 to 2014-04-09 10:00 | 2014-06-06 15:00 to 2020-12-29 03:00 | 2021-01-15 03:00 to 2025-08-08 08:00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -656,12 +656,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00</t>
+          <t>2012-01-02 03:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -677,7 +677,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00 to 2025-08-08 02:00</t>
+          <t>2012-01-02 03:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2014-08-05 07:00</t>
+          <t>2014-08-05 18:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -718,12 +718,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-03-13 07:00 to 2024-03-25 10:00 (12.12 days)</t>
+          <t>2024-03-13 18:00 to 2024-03-25 21:00 (12.12 days)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2014-08-05 07:00 to 2024-03-13 07:00 | 2024-03-25 10:00 to 2025-08-08 02:00</t>
+          <t>2014-08-05 18:00 to 2024-03-13 18:00 | 2024-03-25 21:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -740,12 +740,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2013-09-20 10:00</t>
+          <t>2013-09-20 21:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -761,7 +761,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2013-09-20 10:00 to 2025-08-08 02:00</t>
+          <t>2013-09-20 21:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2012-01-01 14:00</t>
+          <t>2012-01-02 01:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2025-08-08 05:00</t>
+          <t>2025-08-08 16:00</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -802,12 +802,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2021-06-04 06:00 to 2021-06-11 11:00 (7.21 days)</t>
+          <t>2021-06-04 17:00 to 2021-06-11 22:00 (7.21 days)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2012-01-01 14:00 to 2021-06-04 06:00 | 2021-06-11 11:00 to 2025-08-08 05:00</t>
+          <t>2012-01-02 01:00 to 2021-06-04 17:00 | 2021-06-11 22:00 to 2025-08-08 16:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2014-10-02 05:00</t>
+          <t>2014-10-02 16:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2025-08-08 01:00</t>
+          <t>2025-08-08 12:00</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -848,12 +848,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2020-12-28 19:00 to 2021-01-14 07:00 (16.50 days) | 2021-06-15 10:00 to 2021-07-02 20:00 (17.42 days) | 2024-01-08 05:00 to 2024-01-16 14:00 (8.38 days) | 2024-06-23 06:00 to 2024-07-03 09:00 (10.12 days)</t>
+          <t>2020-12-29 06:00 to 2021-01-14 18:00 (16.50 days) | 2021-06-15 21:00 to 2021-07-03 07:00 (17.42 days) | 2024-01-08 16:00 to 2024-01-17 01:00 (8.38 days) | 2024-06-23 17:00 to 2024-07-03 20:00 (10.12 days)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2014-10-02 05:00 to 2020-12-28 19:00 | 2021-01-14 07:00 to 2021-06-15 10:00 | 2021-07-02 20:00 to 2024-01-08 05:00 | 2024-01-16 14:00 to 2024-06-23 06:00 | 2024-07-03 09:00 to 2025-08-08 01:00</t>
+          <t>2014-10-02 16:00 to 2020-12-29 06:00 | 2021-01-14 18:00 to 2021-06-15 21:00 | 2021-07-03 07:00 to 2024-01-08 16:00 | 2024-01-17 01:00 to 2024-06-23 17:00 | 2024-07-03 20:00 to 2025-08-08 12:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00</t>
+          <t>2012-01-02 03:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -891,7 +891,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00 to 2025-08-08 02:00</t>
+          <t>2012-01-02 03:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2012-09-11 10:00</t>
+          <t>2012-09-11 21:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -929,7 +929,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2012-09-11 10:00 to 2025-08-08 02:00</t>
+          <t>2012-09-11 21:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2013-02-06 18:00</t>
+          <t>2013-02-07 05:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -967,7 +967,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2013-02-06 18:00 to 2025-08-08 02:00</t>
+          <t>2013-02-07 05:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -984,12 +984,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2012-01-01 20:00</t>
+          <t>2012-01-02 07:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2025-08-07 18:00</t>
+          <t>2025-08-08 05:00</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2020-12-28 20:00 to 2021-01-14 08:00 (16.50 days)</t>
+          <t>2020-12-29 07:00 to 2021-01-14 19:00 (16.50 days)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2012-01-01 20:00 to 2020-12-28 20:00 | 2021-01-14 08:00 to 2025-08-07 18:00</t>
+          <t>2012-01-02 07:00 to 2020-12-29 07:00 | 2021-01-14 19:00 to 2025-08-08 05:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2012-01-01 08:00</t>
+          <t>2012-01-01 19:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2023-12-30 20:00</t>
+          <t>2023-12-31 07:00</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1051,7 +1051,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2012-01-01 08:00 to 2023-12-30 20:00</t>
+          <t>2012-01-01 19:00 to 2023-12-31 07:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2012-01-01 23:00</t>
+          <t>2012-01-02 10:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2023-12-31 03:00</t>
+          <t>2023-12-31 14:00</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2021-02-05 08:00 to 2021-02-19 21:00 (14.54 days)</t>
+          <t>2021-02-05 19:00 to 2021-02-20 08:00 (14.54 days)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2012-01-01 23:00 to 2021-02-05 08:00 | 2021-02-19 21:00 to 2023-12-31 03:00</t>
+          <t>2012-01-02 10:00 to 2021-02-05 19:00 | 2021-02-20 08:00 to 2023-12-31 14:00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2012-01-01 13:00</t>
+          <t>2012-01-02 00:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2023-12-31 07:00</t>
+          <t>2023-12-31 18:00</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2020-12-28 20:00 to 2021-01-14 08:00 (16.50 days) | 2022-07-25 02:00 to 2022-08-01 09:00 (7.29 days)</t>
+          <t>2020-12-29 07:00 to 2021-01-14 19:00 (16.50 days) | 2022-07-25 13:00 to 2022-08-01 20:00 (7.29 days)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2012-01-01 13:00 to 2020-12-28 20:00 | 2021-01-14 08:00 to 2022-07-25 02:00 | 2022-08-01 09:00 to 2023-12-31 07:00</t>
+          <t>2012-01-02 00:00 to 2020-12-29 07:00 | 2021-01-14 19:00 to 2022-07-25 13:00 | 2022-08-01 20:00 to 2023-12-31 18:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00</t>
+          <t>2012-01-02 03:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2023-12-31 02:00</t>
+          <t>2023-12-31 13:00</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2020-12-28 16:00 to 2021-01-15 04:00 (17.50 days)</t>
+          <t>2020-12-29 03:00 to 2021-01-15 15:00 (17.50 days)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00 to 2020-12-28 16:00 | 2021-01-15 04:00 to 2023-12-31 02:00</t>
+          <t>2012-01-02 03:00 to 2020-12-29 03:00 | 2021-01-15 15:00 to 2023-12-31 13:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2012-01-01 19:00</t>
+          <t>2012-01-02 06:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2023-12-31 04:00</t>
+          <t>2023-12-31 15:00</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2012-08-14 09:00 to 2012-08-21 22:00 (7.54 days) | 2020-12-29 00:00 to 2021-01-14 12:00 (16.50 days)</t>
+          <t>2012-08-14 20:00 to 2012-08-22 09:00 (7.54 days) | 2020-12-29 11:00 to 2021-01-14 23:00 (16.50 days)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2012-01-01 19:00 to 2012-08-14 09:00 | 2012-08-21 22:00 to 2020-12-29 00:00 | 2021-01-14 12:00 to 2023-12-31 04:00</t>
+          <t>2012-01-02 06:00 to 2012-08-14 20:00 | 2012-08-22 09:00 to 2020-12-29 11:00 | 2021-01-14 23:00 to 2023-12-31 15:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00</t>
+          <t>2012-01-02 04:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2023-08-15 21:00</t>
+          <t>2023-08-16 08:00</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2018-11-25 08:00 to 2018-12-09 05:00 (13.88 days) | 2020-12-28 21:00 to 2021-01-14 09:00 (16.50 days)</t>
+          <t>2018-11-25 19:00 to 2018-12-09 16:00 (13.88 days) | 2020-12-29 08:00 to 2021-01-14 20:00 (16.50 days)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00 to 2018-11-25 08:00 | 2018-12-09 05:00 to 2020-12-28 21:00 | 2021-01-14 09:00 to 2023-08-15 21:00</t>
+          <t>2012-01-02 04:00 to 2018-11-25 19:00 | 2018-12-09 16:00 to 2020-12-29 08:00 | 2021-01-14 20:00 to 2023-08-16 08:00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2012-01-01 14:00</t>
+          <t>2012-01-02 01:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2023-12-31 06:00</t>
+          <t>2023-12-31 17:00</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2018-05-22 14:00 to 2018-06-29 06:00 (37.67 days) | 2020-12-29 00:00 to 2021-01-14 12:00 (16.50 days) | 2023-04-25 04:00 to 2023-08-25 20:00 (122.67 days)</t>
+          <t>2018-05-23 01:00 to 2018-06-29 17:00 (37.67 days) | 2020-12-29 11:00 to 2021-01-14 23:00 (16.50 days) | 2023-04-25 15:00 to 2023-08-26 07:00 (122.67 days)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2012-01-01 14:00 to 2018-05-22 14:00 | 2018-06-29 06:00 to 2020-12-29 00:00 | 2021-01-14 12:00 to 2023-04-25 04:00 | 2023-08-25 20:00 to 2023-12-31 06:00</t>
+          <t>2012-01-02 01:00 to 2018-05-23 01:00 | 2018-06-29 17:00 to 2020-12-29 11:00 | 2021-01-14 23:00 to 2023-04-25 15:00 | 2023-08-26 07:00 to 2023-12-31 17:00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00</t>
+          <t>2012-01-02 03:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2023-11-27 21:00</t>
+          <t>2023-11-28 08:00</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2020-04-30 20:00 to 2020-05-12 21:00 (12.04 days) | 2020-12-28 21:00 to 2021-01-14 09:00 (16.50 days)</t>
+          <t>2020-05-01 07:00 to 2020-05-13 08:00 (12.04 days) | 2020-12-29 08:00 to 2021-01-14 20:00 (16.50 days)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00 to 2020-04-30 20:00 | 2020-05-12 21:00 to 2020-12-28 21:00 | 2021-01-14 09:00 to 2023-11-27 21:00</t>
+          <t>2012-01-02 03:00 to 2020-05-01 07:00 | 2020-05-13 08:00 to 2020-12-29 08:00 | 2021-01-14 20:00 to 2023-11-28 08:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2012-01-01 19:00</t>
+          <t>2012-01-02 06:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2023-12-31 03:00</t>
+          <t>2023-12-31 14:00</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1411,7 +1411,7 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2012-01-01 19:00 to 2023-12-31 03:00</t>
+          <t>2012-01-02 06:00 to 2023-12-31 14:00</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2012-01-01 09:00</t>
+          <t>2012-01-01 20:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2025-08-07 20:00</t>
+          <t>2025-08-08 07:00</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1449,7 +1449,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2012-01-01 09:00 to 2025-08-07 20:00</t>
+          <t>2012-01-01 20:00 to 2025-08-08 07:00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2013-01-01 15:00</t>
+          <t>2013-01-02 02:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2025-08-07 19:00</t>
+          <t>2025-08-08 06:00</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1490,12 +1490,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2021-06-03 21:00 to 2021-06-11 11:00 (7.58 days) | 2024-07-31 06:00 to 2024-08-07 19:00 (7.54 days)</t>
+          <t>2021-06-04 08:00 to 2021-06-11 22:00 (7.58 days) | 2024-07-31 17:00 to 2024-08-08 06:00 (7.54 days)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2013-01-01 15:00 to 2021-06-03 21:00 | 2021-06-11 11:00 to 2024-07-31 06:00 | 2024-08-07 19:00 to 2025-08-07 19:00</t>
+          <t>2013-01-02 02:00 to 2021-06-04 08:00 | 2021-06-11 22:00 to 2024-07-31 17:00 | 2024-08-08 06:00 to 2025-08-08 06:00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2012-01-01 15:00</t>
+          <t>2012-01-02 02:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2025-08-08 04:00</t>
+          <t>2025-08-08 15:00</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2020-12-29 00:00 to 2021-01-14 12:00 (16.50 days)</t>
+          <t>2020-12-29 11:00 to 2021-01-14 23:00 (16.50 days)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2012-01-01 15:00 to 2020-12-29 00:00 | 2021-01-14 12:00 to 2025-08-08 04:00</t>
+          <t>2012-01-02 02:00 to 2020-12-29 11:00 | 2021-01-14 23:00 to 2025-08-08 15:00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2012-01-01 18:00</t>
+          <t>2012-01-02 05:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2023-12-31 04:00</t>
+          <t>2023-12-31 15:00</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2020-12-29 00:00 to 2021-01-14 12:00 (16.50 days)</t>
+          <t>2020-12-29 11:00 to 2021-01-14 23:00 (16.50 days)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2012-01-01 18:00 to 2020-12-29 00:00 | 2021-01-14 12:00 to 2023-12-31 04:00</t>
+          <t>2012-01-02 05:00 to 2020-12-29 11:00 | 2021-01-14 23:00 to 2023-12-31 15:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2012-01-01 19:00</t>
+          <t>2012-01-02 06:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2023-12-31 05:00</t>
+          <t>2023-12-31 16:00</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2020-12-28 19:00 to 2021-01-14 07:00 (16.50 days)</t>
+          <t>2020-12-29 06:00 to 2021-01-14 18:00 (16.50 days)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2012-01-01 19:00 to 2020-12-28 19:00 | 2021-01-14 07:00 to 2023-12-31 05:00</t>
+          <t>2012-01-02 06:00 to 2020-12-29 06:00 | 2021-01-14 18:00 to 2023-12-31 16:00</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00</t>
+          <t>2012-01-02 04:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2023-12-31 04:00</t>
+          <t>2023-12-31 15:00</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2020-12-28 14:00 to 2021-01-14 14:00 (17.00 days) | 2021-05-25 04:00 to 2021-11-29 21:00 (188.75 days)</t>
+          <t>2020-12-29 01:00 to 2021-01-15 01:00 (17.00 days) | 2021-05-25 15:00 to 2021-11-30 08:00 (188.75 days)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00 to 2020-12-28 14:00 | 2021-01-14 14:00 to 2021-05-25 04:00 | 2021-11-29 21:00 to 2023-12-31 04:00</t>
+          <t>2012-01-02 04:00 to 2020-12-29 01:00 | 2021-01-15 01:00 to 2021-05-25 15:00 | 2021-11-30 08:00 to 2023-12-31 15:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2012-01-01 18:00</t>
+          <t>2012-01-02 05:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2023-12-30 20:00</t>
+          <t>2023-12-31 07:00</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1720,12 +1720,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2020-12-28 15:00 to 2021-01-14 10:00 (16.79 days)</t>
+          <t>2020-12-29 02:00 to 2021-01-14 21:00 (16.79 days)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2012-01-01 18:00 to 2020-12-28 15:00 | 2021-01-14 10:00 to 2023-12-30 20:00</t>
+          <t>2012-01-02 05:00 to 2020-12-29 02:00 | 2021-01-14 21:00 to 2023-12-31 07:00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2012-01-01 09:00</t>
+          <t>2012-01-01 20:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2020-12-31 18:00 to 2021-01-13 21:00 (13.12 days)</t>
+          <t>2021-01-01 05:00 to 2021-01-14 08:00 (13.12 days)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2012-01-01 09:00 to 2020-12-31 18:00 | 2021-01-13 21:00 to 2025-08-08 02:00</t>
+          <t>2012-01-01 20:00 to 2021-01-01 05:00 | 2021-01-14 08:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00</t>
+          <t>2012-01-02 03:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2023-12-31 01:00</t>
+          <t>2023-12-31 12:00</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2013-11-26 01:00 to 2013-12-06 09:00 (10.33 days) | 2020-12-31 18:00 to 2021-01-15 04:00 (14.42 days)</t>
+          <t>2013-11-26 12:00 to 2013-12-06 20:00 (10.33 days) | 2021-01-01 05:00 to 2021-01-15 15:00 (14.42 days)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00 to 2013-11-26 01:00 | 2013-12-06 09:00 to 2020-12-31 18:00 | 2021-01-15 04:00 to 2023-12-31 01:00</t>
+          <t>2012-01-02 03:00 to 2013-11-26 12:00 | 2013-12-06 20:00 to 2021-01-01 05:00 | 2021-01-15 15:00 to 2023-12-31 12:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2012-01-01 14:00</t>
+          <t>2012-01-02 01:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2025-08-08 05:00</t>
+          <t>2025-08-08 16:00</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1858,12 +1858,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2020-12-28 17:00 to 2021-01-15 05:00 (17.50 days) | 2023-06-02 07:00 to 2023-06-09 19:00 (7.50 days) | 2023-12-19 13:00 to 2024-01-02 14:00 (14.04 days) | 2024-01-02 14:00 to 2024-01-13 14:00 (11.00 days) | 2024-01-23 14:00 to 2024-02-07 04:00 (14.58 days) | 2024-09-16 05:00 to 2024-09-26 19:00 (10.58 days)</t>
+          <t>2020-12-29 04:00 to 2021-01-15 16:00 (17.50 days) | 2023-06-02 18:00 to 2023-06-10 06:00 (7.50 days) | 2023-12-20 00:00 to 2024-01-03 01:00 (14.04 days) | 2024-01-03 01:00 to 2024-01-14 01:00 (11.00 days) | 2024-01-24 01:00 to 2024-02-07 15:00 (14.58 days) | 2024-09-16 16:00 to 2024-09-27 06:00 (10.58 days)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2012-01-01 14:00 to 2020-12-28 17:00 | 2021-01-15 05:00 to 2023-06-02 07:00 | 2023-06-09 19:00 to 2023-12-19 13:00 | 2024-01-02 14:00 to 2024-01-02 14:00 | 2024-01-13 14:00 to 2024-01-23 14:00 | 2024-02-07 04:00 to 2024-09-16 05:00 | 2024-09-26 19:00 to 2025-08-08 05:00</t>
+          <t>2012-01-02 01:00 to 2020-12-29 04:00 | 2021-01-15 16:00 to 2023-06-02 18:00 | 2023-06-10 06:00 to 2023-12-20 00:00 | 2024-01-03 01:00 to 2024-01-03 01:00 | 2024-01-14 01:00 to 2024-01-24 01:00 | 2024-02-07 15:00 to 2024-09-16 16:00 | 2024-09-27 06:00 to 2025-08-08 16:00</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2014-07-25 05:00</t>
+          <t>2014-07-25 16:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2020-10-11 22:00 to 2021-09-20 07:00 (343.38 days)</t>
+          <t>2020-10-12 09:00 to 2021-09-20 18:00 (343.38 days)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2014-07-25 05:00 to 2020-10-11 22:00 | 2021-09-20 07:00 to 2025-08-08 02:00</t>
+          <t>2014-07-25 16:00 to 2020-10-12 09:00 | 2021-09-20 18:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00</t>
+          <t>2012-01-02 04:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2025-08-08 06:00</t>
+          <t>2025-08-08 17:00</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2021-05-28 09:00 to 2021-06-07 09:00 (10.00 days)</t>
+          <t>2021-05-28 20:00 to 2021-06-07 20:00 (10.00 days)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00 to 2021-05-28 09:00 | 2021-06-07 09:00 to 2025-08-08 06:00</t>
+          <t>2012-01-02 04:00 to 2021-05-28 20:00 | 2021-06-07 20:00 to 2025-08-08 17:00</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1972,12 +1972,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2012-01-01 13:00</t>
+          <t>2012-01-02 00:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2020-12-28 20:00 to 2021-01-14 08:00 (16.50 days) | 2025-03-17 05:00 to 2025-03-28 14:00 (11.38 days)</t>
+          <t>2020-12-29 07:00 to 2021-01-14 19:00 (16.50 days) | 2025-03-17 16:00 to 2025-03-29 01:00 (11.38 days)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2012-01-01 13:00 to 2020-12-28 20:00 | 2021-01-14 08:00 to 2025-03-17 05:00 | 2025-03-28 14:00 to 2025-08-08 02:00</t>
+          <t>2012-01-02 00:00 to 2020-12-29 07:00 | 2021-01-14 19:00 to 2025-03-17 16:00 | 2025-03-29 01:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00</t>
+          <t>2012-01-02 04:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2025-08-08 04:00</t>
+          <t>2025-08-08 15:00</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2020-12-29 00:00 to 2021-01-14 12:00 (16.50 days)</t>
+          <t>2020-12-29 11:00 to 2021-01-14 23:00 (16.50 days)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00 to 2020-12-29 00:00 | 2021-01-14 12:00 to 2025-08-08 04:00</t>
+          <t>2012-01-02 04:00 to 2020-12-29 11:00 | 2021-01-14 23:00 to 2025-08-08 15:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00</t>
+          <t>2012-01-02 03:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2020-12-28 16:00 to 2021-01-14 16:00 (17.00 days) | 2022-06-28 09:00 to 2022-07-07 17:00 (9.33 days)</t>
+          <t>2020-12-29 03:00 to 2021-01-15 03:00 (17.00 days) | 2022-06-28 20:00 to 2022-07-08 04:00 (9.33 days)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00 to 2020-12-28 16:00 | 2021-01-14 16:00 to 2022-06-28 09:00 | 2022-07-07 17:00 to 2025-08-08 02:00</t>
+          <t>2012-01-02 03:00 to 2020-12-29 03:00 | 2021-01-15 03:00 to 2022-06-28 20:00 | 2022-07-08 04:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2012-01-01 13:00</t>
+          <t>2012-01-02 00:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2025-08-08 05:00</t>
+          <t>2025-08-08 16:00</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2015-01-15 19:00 to 2015-01-23 08:00 (7.54 days) | 2017-01-03 08:00 to 2017-01-18 08:00 (15.00 days) | 2020-12-28 19:00 to 2021-01-14 07:00 (16.50 days) | 2022-10-11 23:00 to 2022-10-19 06:00 (7.29 days)</t>
+          <t>2015-01-16 06:00 to 2015-01-23 19:00 (7.54 days) | 2017-01-03 19:00 to 2017-01-18 19:00 (15.00 days) | 2020-12-29 06:00 to 2021-01-14 18:00 (16.50 days) | 2022-10-12 10:00 to 2022-10-19 17:00 (7.29 days)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2012-01-01 13:00 to 2015-01-15 19:00 | 2015-01-23 08:00 to 2017-01-03 08:00 | 2017-01-18 08:00 to 2020-12-28 19:00 | 2021-01-14 07:00 to 2022-10-11 23:00 | 2022-10-19 06:00 to 2025-08-08 05:00</t>
+          <t>2012-01-02 00:00 to 2015-01-16 06:00 | 2015-01-23 19:00 to 2017-01-03 19:00 | 2017-01-18 19:00 to 2020-12-29 06:00 | 2021-01-14 18:00 to 2022-10-12 10:00 | 2022-10-19 17:00 to 2025-08-08 16:00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2012-01-01 14:00</t>
+          <t>2012-01-02 01:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2025-08-08 05:00</t>
+          <t>2025-08-08 16:00</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2020-07-22 02:00 to 2020-07-29 05:00 (7.12 days) | 2020-12-29 00:00 to 2021-01-14 12:00 (16.50 days)</t>
+          <t>2020-07-22 13:00 to 2020-07-29 16:00 (7.12 days) | 2020-12-29 11:00 to 2021-01-14 23:00 (16.50 days)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2012-01-01 14:00 to 2020-07-22 02:00 | 2020-07-29 05:00 to 2020-12-29 00:00 | 2021-01-14 12:00 to 2025-08-08 05:00</t>
+          <t>2012-01-02 01:00 to 2020-07-22 13:00 | 2020-07-29 16:00 to 2020-12-29 11:00 | 2021-01-14 23:00 to 2025-08-08 16:00</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2012-01-01 19:00</t>
+          <t>2012-01-02 06:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2023-12-31 03:00</t>
+          <t>2023-12-31 14:00</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2012-03-26 02:00 to 2012-12-11 08:00 (260.29 days) | 2016-01-08 05:00 to 2016-01-15 10:00 (7.21 days) | 2020-12-31 18:00 to 2021-01-14 06:00 (13.50 days)</t>
+          <t>2012-03-26 13:00 to 2012-12-11 19:00 (260.29 days) | 2016-01-08 16:00 to 2016-01-15 21:00 (7.21 days) | 2021-01-01 05:00 to 2021-01-14 17:00 (13.50 days)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2012-01-01 19:00 to 2012-03-26 02:00 | 2012-12-11 08:00 to 2016-01-08 05:00 | 2016-01-15 10:00 to 2020-12-31 18:00 | 2021-01-14 06:00 to 2023-12-31 03:00</t>
+          <t>2012-01-02 06:00 to 2012-03-26 13:00 | 2012-12-11 19:00 to 2016-01-08 16:00 | 2016-01-15 21:00 to 2021-01-01 05:00 | 2021-01-14 17:00 to 2023-12-31 14:00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00</t>
+          <t>2012-01-02 03:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2023-12-31 04:00</t>
+          <t>2023-12-31 15:00</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2272,12 +2272,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2020-12-28 17:00 to 2021-01-15 05:00 (17.50 days)</t>
+          <t>2020-12-29 04:00 to 2021-01-15 16:00 (17.50 days)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00 to 2020-12-28 17:00 | 2021-01-15 05:00 to 2023-12-31 04:00</t>
+          <t>2012-01-02 03:00 to 2020-12-29 04:00 | 2021-01-15 16:00 to 2023-12-31 15:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2012-01-01 18:00</t>
+          <t>2012-01-02 05:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -2318,12 +2318,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2020-12-29 00:00 to 2021-01-14 12:00 (16.50 days)</t>
+          <t>2020-12-29 11:00 to 2021-01-14 23:00 (16.50 days)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2012-01-01 18:00 to 2020-12-29 00:00 | 2021-01-14 12:00 to 2025-08-08 02:00</t>
+          <t>2012-01-02 05:00 to 2020-12-29 11:00 | 2021-01-14 23:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00</t>
+          <t>2012-01-02 04:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2020-12-28 21:00 to 2021-01-14 09:00 (16.50 days) | 2025-01-03 00:00 to 2025-01-17 07:00 (14.29 days)</t>
+          <t>2020-12-29 08:00 to 2021-01-14 20:00 (16.50 days) | 2025-01-03 11:00 to 2025-01-17 18:00 (14.29 days)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00 to 2020-12-28 21:00 | 2021-01-14 09:00 to 2025-01-03 00:00 | 2025-01-17 07:00 to 2025-08-08 02:00</t>
+          <t>2012-01-02 04:00 to 2020-12-29 08:00 | 2021-01-14 20:00 to 2025-01-03 11:00 | 2025-01-17 18:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2012-01-01 15:00</t>
+          <t>2012-01-02 02:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2023-12-31 02:00</t>
+          <t>2023-12-31 13:00</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2013-05-09 13:00 to 2013-05-17 18:00 (8.21 days) | 2014-08-31 18:00 to 2014-09-09 06:00 (8.50 days) | 2016-12-18 18:00 to 2017-01-01 06:00 (13.50 days) | 2018-07-30 16:00 to 2018-08-07 03:00 (7.46 days) | 2018-11-30 18:00 to 2018-12-15 04:00 (14.42 days) | 2018-12-31 02:00 to 2019-01-07 04:00 (7.08 days) | 2019-01-11 09:00 to 2019-01-27 18:00 (16.38 days) | 2019-07-29 16:00 to 2019-08-16 08:00 (17.67 days) | 2019-09-01 09:00 to 2019-09-09 09:00 (8.00 days) | 2019-11-10 23:00 to 2019-11-28 10:00 (17.46 days) | 2019-12-18 08:00 to 2019-12-25 15:00 (7.29 days) | 2020-01-17 03:00 to 2020-01-28 03:00 (11.00 days) | 2020-06-25 05:00 to 2020-07-24 08:00 (29.12 days) | 2020-11-18 19:00 to 2020-12-04 15:00 (15.83 days) | 2020-12-08 15:00 to 2020-12-16 09:00 (7.75 days)</t>
+          <t>2013-05-10 00:00 to 2013-05-18 05:00 (8.21 days) | 2014-09-01 05:00 to 2014-09-09 17:00 (8.50 days) | 2016-12-19 05:00 to 2017-01-01 17:00 (13.50 days) | 2018-07-31 03:00 to 2018-08-07 14:00 (7.46 days) | 2018-12-01 05:00 to 2018-12-15 15:00 (14.42 days) | 2018-12-31 13:00 to 2019-01-07 15:00 (7.08 days) | 2019-01-11 20:00 to 2019-01-28 05:00 (16.38 days) | 2019-07-30 03:00 to 2019-08-16 19:00 (17.67 days) | 2019-09-01 20:00 to 2019-09-09 20:00 (8.00 days) | 2019-11-11 10:00 to 2019-11-28 21:00 (17.46 days) | 2019-12-18 19:00 to 2019-12-26 02:00 (7.29 days) | 2020-01-17 14:00 to 2020-01-28 14:00 (11.00 days) | 2020-06-25 16:00 to 2020-07-24 19:00 (29.12 days) | 2020-11-19 06:00 to 2020-12-05 02:00 (15.83 days) | 2020-12-09 02:00 to 2020-12-16 20:00 (7.75 days)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2012-01-01 15:00 to 2013-05-09 13:00 | 2013-05-17 18:00 to 2014-08-31 18:00 | 2014-09-09 06:00 to 2016-12-18 18:00 | 2017-01-01 06:00 to 2018-07-30 16:00 | 2018-08-07 03:00 to 2018-11-30 18:00 | 2018-12-15 04:00 to 2018-12-31 02:00 | 2019-01-07 04:00 to 2019-01-11 09:00 | 2019-01-27 18:00 to 2019-07-29 16:00 | 2019-08-16 08:00 to 2019-09-01 09:00 | 2019-09-09 09:00 to 2019-11-10 23:00 | 2019-11-28 10:00 to 2019-12-18 08:00 | 2019-12-25 15:00 to 2020-01-17 03:00 | 2020-01-28 03:00 to 2020-06-25 05:00 | 2020-07-24 08:00 to 2020-11-18 19:00 | 2020-12-04 15:00 to 2020-12-08 15:00 | 2020-12-16 09:00 to 2023-12-31 02:00</t>
+          <t>2012-01-02 02:00 to 2013-05-10 00:00 | 2013-05-18 05:00 to 2014-09-01 05:00 | 2014-09-09 17:00 to 2016-12-19 05:00 | 2017-01-01 17:00 to 2018-07-31 03:00 | 2018-08-07 14:00 to 2018-12-01 05:00 | 2018-12-15 15:00 to 2018-12-31 13:00 | 2019-01-07 15:00 to 2019-01-11 20:00 | 2019-01-28 05:00 to 2019-07-30 03:00 | 2019-08-16 19:00 to 2019-09-01 20:00 | 2019-09-09 20:00 to 2019-11-11 10:00 | 2019-11-28 21:00 to 2019-12-18 19:00 | 2019-12-26 02:00 to 2020-01-17 14:00 | 2020-01-28 14:00 to 2020-06-25 16:00 | 2020-07-24 19:00 to 2020-11-19 06:00 | 2020-12-05 02:00 to 2020-12-09 02:00 | 2020-12-16 20:00 to 2023-12-31 13:00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2012-01-01 14:00</t>
+          <t>2012-01-02 01:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2023-12-31 03:00</t>
+          <t>2023-12-31 14:00</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2456,12 +2456,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2021-02-06 17:00 to 2021-02-22 04:00 (15.46 days) | 2022-12-19 05:00 to 2022-12-29 15:00 (10.42 days)</t>
+          <t>2021-02-07 04:00 to 2021-02-22 15:00 (15.46 days) | 2022-12-19 16:00 to 2022-12-30 02:00 (10.42 days)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2012-01-01 14:00 to 2021-02-06 17:00 | 2021-02-22 04:00 to 2022-12-19 05:00 | 2022-12-29 15:00 to 2023-12-31 03:00</t>
+          <t>2012-01-02 01:00 to 2021-02-07 04:00 | 2021-02-22 15:00 to 2022-12-19 16:00 | 2022-12-30 02:00 to 2023-12-31 14:00</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2012-01-01 14:00</t>
+          <t>2012-01-02 01:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2023-12-31 07:00</t>
+          <t>2023-12-31 18:00</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2019-10-30 05:00 to 2019-11-08 20:00 (9.67 days) | 2020-01-16 09:00 to 2020-02-12 07:00 (26.92 days)</t>
+          <t>2019-10-30 16:00 to 2019-11-09 07:00 (9.67 days) | 2020-01-16 20:00 to 2020-02-12 18:00 (26.92 days)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2012-01-01 14:00 to 2019-10-30 05:00 | 2019-11-08 20:00 to 2020-01-16 09:00 | 2020-02-12 07:00 to 2023-12-31 07:00</t>
+          <t>2012-01-02 01:00 to 2019-10-30 16:00 | 2019-11-09 07:00 to 2020-01-16 20:00 | 2020-02-12 18:00 to 2023-12-31 18:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2012-01-02 09:00</t>
+          <t>2012-01-02 20:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2023-11-25 17:00</t>
+          <t>2023-11-26 04:00</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2017-08-06 08:00 to 2017-08-15 07:00 (8.96 days) | 2017-08-30 20:00 to 2017-09-07 05:00 (7.38 days) | 2019-01-16 18:00 to 2019-02-15 06:00 (29.50 days) | 2020-12-08 06:00 to 2021-02-23 18:00 (77.50 days) | 2021-07-13 20:00 to 2021-07-28 23:00 (15.12 days)</t>
+          <t>2017-08-06 19:00 to 2017-08-15 18:00 (8.96 days) | 2017-08-31 07:00 to 2017-09-07 16:00 (7.38 days) | 2019-01-17 05:00 to 2019-02-15 17:00 (29.50 days) | 2020-12-08 17:00 to 2021-02-24 05:00 (77.50 days) | 2021-07-14 07:00 to 2021-07-29 10:00 (15.12 days)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2012-01-02 09:00 to 2017-08-06 08:00 | 2017-08-15 07:00 to 2017-08-30 20:00 | 2017-09-07 05:00 to 2019-01-16 18:00 | 2019-02-15 06:00 to 2020-12-08 06:00 | 2021-02-23 18:00 to 2021-07-13 20:00 | 2021-07-28 23:00 to 2023-11-25 17:00</t>
+          <t>2012-01-02 20:00 to 2017-08-06 19:00 | 2017-08-15 18:00 to 2017-08-31 07:00 | 2017-09-07 16:00 to 2019-01-17 05:00 | 2019-02-15 17:00 to 2020-12-08 17:00 | 2021-02-24 05:00 to 2021-07-14 07:00 | 2021-07-29 10:00 to 2023-11-26 04:00</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2012-01-01 12:00</t>
+          <t>2012-01-01 23:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2023-12-30 20:00</t>
+          <t>2023-12-31 07:00</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2591,7 +2591,7 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2012-01-01 12:00 to 2023-12-30 20:00</t>
+          <t>2012-01-01 23:00 to 2023-12-31 07:00</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2014-05-27 08:00</t>
+          <t>2014-05-27 19:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2025-08-07 19:00</t>
+          <t>2025-08-08 06:00</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2020-12-28 19:00 to 2021-01-14 09:00 (16.58 days)</t>
+          <t>2020-12-29 06:00 to 2021-01-14 20:00 (16.58 days)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2014-05-27 08:00 to 2020-12-28 19:00 | 2021-01-14 09:00 to 2025-08-07 19:00</t>
+          <t>2014-05-27 19:00 to 2020-12-29 06:00 | 2021-01-14 20:00 to 2025-08-08 06:00</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2654,12 +2654,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2012-01-01 11:00</t>
+          <t>2012-01-01 22:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2020-12-28 17:00 to 2021-01-14 17:00 (17.00 days)</t>
+          <t>2020-12-29 04:00 to 2021-01-15 04:00 (17.00 days)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2012-01-01 11:00 to 2020-12-28 17:00 | 2021-01-14 17:00 to 2025-08-08 02:00</t>
+          <t>2012-01-01 22:00 to 2020-12-29 04:00 | 2021-01-15 04:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2012-01-01 12:00</t>
+          <t>2012-01-01 23:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2020-12-28 21:00 to 2021-01-14 09:00 (16.50 days)</t>
+          <t>2020-12-29 08:00 to 2021-01-14 20:00 (16.50 days)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2012-01-01 12:00 to 2020-12-28 21:00 | 2021-01-14 09:00 to 2025-08-08 02:00</t>
+          <t>2012-01-01 23:00 to 2020-12-29 08:00 | 2021-01-14 20:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2012-01-01 14:00</t>
+          <t>2012-01-02 01:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2025-08-07 20:00</t>
+          <t>2025-08-08 07:00</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2019-01-23 12:00 to 2019-02-01 00:00 (8.50 days) | 2022-01-17 07:00 to 2022-01-25 06:00 (7.96 days) | 2023-05-26 07:00 to 2023-06-08 17:00 (13.42 days) | 2023-12-20 07:00 to 2024-01-07 07:00 (18.00 days) | 2024-01-07 07:00 to 2024-02-06 04:00 (29.88 days)</t>
+          <t>2019-01-23 23:00 to 2019-02-01 11:00 (8.50 days) | 2022-01-17 18:00 to 2022-01-25 17:00 (7.96 days) | 2023-05-26 18:00 to 2023-06-09 04:00 (13.42 days) | 2023-12-20 18:00 to 2024-01-07 18:00 (18.00 days) | 2024-01-07 18:00 to 2024-02-06 15:00 (29.88 days)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2012-01-01 14:00 to 2019-01-23 12:00 | 2019-02-01 00:00 to 2022-01-17 07:00 | 2022-01-25 06:00 to 2023-05-26 07:00 | 2023-06-08 17:00 to 2023-12-20 07:00 | 2024-01-07 07:00 to 2024-01-07 07:00 | 2024-02-06 04:00 to 2025-08-07 20:00</t>
+          <t>2012-01-02 01:00 to 2019-01-23 23:00 | 2019-02-01 11:00 to 2022-01-17 18:00 | 2022-01-25 17:00 to 2023-05-26 18:00 | 2023-06-09 04:00 to 2023-12-20 18:00 | 2024-01-07 18:00 to 2024-01-07 18:00 | 2024-02-06 15:00 to 2025-08-08 07:00</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2015-11-23 22:00</t>
+          <t>2015-11-24 09:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2025-08-07 20:00</t>
+          <t>2025-08-08 07:00</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2020-12-28 20:00 to 2021-01-14 08:00 (16.50 days) | 2022-12-19 22:00 to 2022-12-28 16:00 (8.75 days)</t>
+          <t>2020-12-29 07:00 to 2021-01-14 19:00 (16.50 days) | 2022-12-20 09:00 to 2022-12-29 03:00 (8.75 days)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2015-11-23 22:00 to 2020-12-28 20:00 | 2021-01-14 08:00 to 2022-12-19 22:00 | 2022-12-28 16:00 to 2025-08-07 20:00</t>
+          <t>2015-11-24 09:00 to 2020-12-29 07:00 | 2021-01-14 19:00 to 2022-12-20 09:00 | 2022-12-29 03:00 to 2025-08-08 07:00</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2012-01-01 11:00</t>
+          <t>2012-01-01 22:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2025-08-07 20:00</t>
+          <t>2025-08-08 07:00</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2020-12-29 00:00 to 2021-01-14 12:00 (16.50 days) | 2021-09-19 14:00 to 2021-09-27 14:00 (8.00 days)</t>
+          <t>2020-12-29 11:00 to 2021-01-14 23:00 (16.50 days) | 2021-09-20 01:00 to 2021-09-28 01:00 (8.00 days)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2012-01-01 11:00 to 2020-12-29 00:00 | 2021-01-14 12:00 to 2021-09-19 14:00 | 2021-09-27 14:00 to 2025-08-07 20:00</t>
+          <t>2012-01-01 22:00 to 2020-12-29 11:00 | 2021-01-14 23:00 to 2021-09-20 01:00 | 2021-09-28 01:00 to 2025-08-08 07:00</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -2884,12 +2884,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00</t>
+          <t>2012-01-02 04:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2905,7 +2905,7 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00 to 2025-08-08 02:00</t>
+          <t>2012-01-02 04:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2012-01-01 12:00</t>
+          <t>2012-01-01 23:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2025-08-07 21:00</t>
+          <t>2025-08-08 08:00</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2014-01-28 05:00 to 2014-02-12 04:00 (14.96 days) | 2020-12-28 20:00 to 2021-01-14 08:00 (16.50 days)</t>
+          <t>2014-01-28 16:00 to 2014-02-12 15:00 (14.96 days) | 2020-12-29 07:00 to 2021-01-14 19:00 (16.50 days)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2012-01-01 12:00 to 2014-01-28 05:00 | 2014-02-12 04:00 to 2020-12-28 20:00 | 2021-01-14 08:00 to 2025-08-07 21:00</t>
+          <t>2012-01-01 23:00 to 2014-01-28 16:00 | 2014-02-12 15:00 to 2020-12-29 07:00 | 2021-01-14 19:00 to 2025-08-08 08:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2012-01-01 18:00</t>
+          <t>2012-01-02 05:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2989,7 +2989,7 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2012-01-01 18:00 to 2025-08-08 02:00</t>
+          <t>2012-01-02 05:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3006,12 +3006,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00</t>
+          <t>2012-01-02 03:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2025-08-08 05:00</t>
+          <t>2025-08-08 16:00</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -3027,7 +3027,7 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00 to 2025-08-08 05:00</t>
+          <t>2012-01-02 03:00 to 2025-08-08 16:00</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00</t>
+          <t>2012-01-02 04:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2025-08-07 19:00</t>
+          <t>2025-08-08 06:00</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2020-12-29 00:00 to 2021-01-14 12:00 (16.50 days)</t>
+          <t>2020-12-29 11:00 to 2021-01-14 23:00 (16.50 days)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00 to 2020-12-29 00:00 | 2021-01-14 12:00 to 2025-08-07 19:00</t>
+          <t>2012-01-02 04:00 to 2020-12-29 11:00 | 2021-01-14 23:00 to 2025-08-08 06:00</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2012-01-01 18:00</t>
+          <t>2012-01-02 05:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2025-08-08 06:00</t>
+          <t>2025-08-08 17:00</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -3114,12 +3114,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2020-12-29 00:00 to 2021-01-14 12:00 (16.50 days) | 2021-11-08 00:00 to 2021-11-30 12:00 (22.50 days)</t>
+          <t>2020-12-29 11:00 to 2021-01-14 23:00 (16.50 days) | 2021-11-08 11:00 to 2021-11-30 23:00 (22.50 days)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2012-01-01 18:00 to 2020-12-29 00:00 | 2021-01-14 12:00 to 2021-11-08 00:00 | 2021-11-30 12:00 to 2025-08-08 06:00</t>
+          <t>2012-01-02 05:00 to 2020-12-29 11:00 | 2021-01-14 23:00 to 2021-11-08 11:00 | 2021-11-30 23:00 to 2025-08-08 17:00</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00</t>
+          <t>2012-01-02 03:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2025-08-08 06:00</t>
+          <t>2025-08-08 17:00</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2016-01-02 09:00 to 2016-02-03 09:00 (32.00 days) | 2016-12-17 00:00 to 2017-01-05 00:00 (19.00 days) | 2018-03-10 16:00 to 2018-07-04 09:00 (115.67 days) | 2020-12-28 19:00 to 2021-01-14 07:00 (16.50 days)</t>
+          <t>2016-01-02 20:00 to 2016-02-03 20:00 (32.00 days) | 2016-12-17 11:00 to 2017-01-05 11:00 (19.00 days) | 2018-03-11 04:00 to 2018-07-04 20:00 (115.67 days) | 2020-12-29 06:00 to 2021-01-14 18:00 (16.50 days)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00 to 2016-01-02 09:00 | 2016-02-03 09:00 to 2016-12-17 00:00 | 2017-01-05 00:00 to 2018-03-10 16:00 | 2018-07-04 09:00 to 2020-12-28 19:00 | 2021-01-14 07:00 to 2025-08-08 06:00</t>
+          <t>2012-01-02 03:00 to 2016-01-02 20:00 | 2016-02-03 20:00 to 2016-12-17 11:00 | 2017-01-05 11:00 to 2018-03-11 04:00 | 2018-07-04 20:00 to 2020-12-29 06:00 | 2021-01-14 18:00 to 2025-08-08 17:00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2012-01-01 19:00</t>
+          <t>2012-01-02 06:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2025-08-07 19:00</t>
+          <t>2025-08-08 06:00</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2012-08-14 17:00 to 2012-08-23 22:00 (9.21 days) | 2018-01-09 06:00 to 2018-01-18 07:00 (9.04 days) | 2020-12-28 20:00 to 2021-01-17 16:00 (19.83 days) | 2022-07-20 06:00 to 2022-08-01 18:00 (12.50 days) | 2024-01-11 08:00 to 2024-02-05 18:00 (25.42 days)</t>
+          <t>2012-08-15 04:00 to 2012-08-24 09:00 (9.21 days) | 2018-01-09 17:00 to 2018-01-18 18:00 (9.04 days) | 2020-12-29 07:00 to 2021-01-18 03:00 (19.83 days) | 2022-07-20 17:00 to 2022-08-02 05:00 (12.50 days) | 2024-01-11 19:00 to 2024-02-06 05:00 (25.42 days)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2012-01-01 19:00 to 2012-08-14 17:00 | 2012-08-23 22:00 to 2018-01-09 06:00 | 2018-01-18 07:00 to 2020-12-28 20:00 | 2021-01-17 16:00 to 2022-07-20 06:00 | 2022-08-01 18:00 to 2024-01-11 08:00 | 2024-02-05 18:00 to 2025-08-07 19:00</t>
+          <t>2012-01-02 06:00 to 2012-08-15 04:00 | 2012-08-24 09:00 to 2018-01-09 17:00 | 2018-01-18 18:00 to 2020-12-29 07:00 | 2021-01-18 03:00 to 2022-07-20 17:00 | 2022-08-02 05:00 to 2024-01-11 19:00 | 2024-02-06 05:00 to 2025-08-08 06:00</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00</t>
+          <t>2012-01-02 03:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -3252,12 +3252,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2020-01-15 07:00 to 2020-02-01 07:00 (17.00 days) | 2020-12-26 08:00 to 2021-01-29 04:00 (33.83 days) | 2025-01-30 23:00 to 2025-02-24 04:00 (24.21 days)</t>
+          <t>2020-01-15 18:00 to 2020-02-01 18:00 (17.00 days) | 2020-12-26 19:00 to 2021-01-29 15:00 (33.83 days) | 2025-01-31 10:00 to 2025-02-24 15:00 (24.21 days)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00 to 2020-01-15 07:00 | 2020-02-01 07:00 to 2020-12-26 08:00 | 2021-01-29 04:00 to 2025-01-30 23:00 | 2025-02-24 04:00 to 2025-08-08 02:00</t>
+          <t>2012-01-02 03:00 to 2020-01-15 18:00 | 2020-02-01 18:00 to 2020-12-26 19:00 | 2021-01-29 15:00 to 2025-01-31 10:00 | 2025-02-24 15:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2012-01-01 14:00</t>
+          <t>2012-01-02 01:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2020-12-28 16:00 to 2021-01-14 16:00 (17.00 days) | 2021-05-25 06:00 to 2021-06-03 05:00 (8.96 days)</t>
+          <t>2020-12-29 03:00 to 2021-01-15 03:00 (17.00 days) | 2021-05-25 17:00 to 2021-06-03 16:00 (8.96 days)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2012-01-01 14:00 to 2020-12-28 16:00 | 2021-01-14 16:00 to 2021-05-25 06:00 | 2021-06-03 05:00 to 2025-08-08 02:00</t>
+          <t>2012-01-02 01:00 to 2020-12-29 03:00 | 2021-01-15 03:00 to 2021-05-25 17:00 | 2021-06-03 16:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2012-01-01 19:00</t>
+          <t>2012-01-02 06:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2012-05-07 17:00 to 2012-06-06 06:00 (29.54 days) | 2020-12-28 21:00 to 2021-01-14 09:00 (16.50 days)</t>
+          <t>2012-05-08 04:00 to 2012-06-06 17:00 (29.54 days) | 2020-12-29 08:00 to 2021-01-14 20:00 (16.50 days)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2012-01-01 19:00 to 2012-05-07 17:00 | 2012-06-06 06:00 to 2020-12-28 21:00 | 2021-01-14 09:00 to 2025-08-08 02:00</t>
+          <t>2012-01-02 06:00 to 2012-05-08 04:00 | 2012-06-06 17:00 to 2020-12-29 08:00 | 2021-01-14 20:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2012-01-01 18:00</t>
+          <t>2012-01-02 05:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2025-08-07 18:00</t>
+          <t>2025-08-08 05:00</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -3390,12 +3390,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2019-07-09 05:00 to 2019-07-16 21:00 (7.67 days) | 2020-12-28 15:00 to 2021-01-14 15:00 (17.00 days)</t>
+          <t>2019-07-09 16:00 to 2019-07-17 08:00 (7.67 days) | 2020-12-29 02:00 to 2021-01-15 02:00 (17.00 days)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2012-01-01 18:00 to 2019-07-09 05:00 | 2019-07-16 21:00 to 2020-12-28 15:00 | 2021-01-14 15:00 to 2025-08-07 18:00</t>
+          <t>2012-01-02 05:00 to 2019-07-09 16:00 | 2019-07-17 08:00 to 2020-12-29 02:00 | 2021-01-15 02:00 to 2025-08-08 05:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3412,12 +3412,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2012-01-01 13:00</t>
+          <t>2012-01-02 00:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2025-08-07 19:00</t>
+          <t>2025-08-08 06:00</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2020-12-28 20:00 to 2021-01-14 08:00 (16.50 days) | 2023-03-20 07:00 to 2023-03-27 20:00 (7.54 days)</t>
+          <t>2020-12-29 07:00 to 2021-01-14 19:00 (16.50 days) | 2023-03-20 18:00 to 2023-03-28 07:00 (7.54 days)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2012-01-01 13:00 to 2020-12-28 20:00 | 2021-01-14 08:00 to 2023-03-20 07:00 | 2023-03-27 20:00 to 2025-08-07 19:00</t>
+          <t>2012-01-02 00:00 to 2020-12-29 07:00 | 2021-01-14 19:00 to 2023-03-20 18:00 | 2023-03-28 07:00 to 2025-08-08 06:00</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3458,12 +3458,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00</t>
+          <t>2012-01-02 04:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2025-08-07 21:00</t>
+          <t>2025-08-08 08:00</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2020-12-28 16:00 to 2021-01-14 16:00 (17.00 days)</t>
+          <t>2020-12-29 03:00 to 2021-01-15 03:00 (17.00 days)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00 to 2020-12-28 16:00 | 2021-01-14 16:00 to 2025-08-07 21:00</t>
+          <t>2012-01-02 04:00 to 2020-12-29 03:00 | 2021-01-15 03:00 to 2025-08-08 08:00</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00</t>
+          <t>2012-01-02 03:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2025-08-08 06:00</t>
+          <t>2025-08-08 17:00</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2018-10-09 02:00 to 2018-10-18 06:00 (9.17 days) | 2020-12-28 20:00 to 2021-01-14 08:00 (16.50 days)</t>
+          <t>2018-10-09 13:00 to 2018-10-18 17:00 (9.17 days) | 2020-12-29 07:00 to 2021-01-14 19:00 (16.50 days)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00 to 2018-10-09 02:00 | 2018-10-18 06:00 to 2020-12-28 20:00 | 2021-01-14 08:00 to 2025-08-08 06:00</t>
+          <t>2012-01-02 03:00 to 2018-10-09 13:00 | 2018-10-18 17:00 to 2020-12-29 07:00 | 2021-01-14 19:00 to 2025-08-08 17:00</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00</t>
+          <t>2012-01-02 03:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2020-12-28 19:00 to 2021-01-14 07:00 (16.50 days)</t>
+          <t>2020-12-29 06:00 to 2021-01-14 18:00 (16.50 days)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00 to 2020-12-28 19:00 | 2021-01-14 07:00 to 2025-08-08 02:00</t>
+          <t>2012-01-02 03:00 to 2020-12-29 06:00 | 2021-01-14 18:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2012-01-01 15:00</t>
+          <t>2012-01-02 02:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2020-12-28 20:00 to 2021-01-14 08:00 (16.50 days)</t>
+          <t>2020-12-29 07:00 to 2021-01-14 19:00 (16.50 days)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2012-01-01 15:00 to 2020-12-28 20:00 | 2021-01-14 08:00 to 2025-08-08 02:00</t>
+          <t>2012-01-02 02:00 to 2020-12-29 07:00 | 2021-01-14 19:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2012-01-01 15:00</t>
+          <t>2012-01-02 02:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2025-08-07 20:00</t>
+          <t>2025-08-08 07:00</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2020-12-31 18:00 to 2021-01-15 05:00 (14.46 days)</t>
+          <t>2021-01-01 05:00 to 2021-01-15 16:00 (14.46 days)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2012-01-01 15:00 to 2020-12-31 18:00 | 2021-01-15 05:00 to 2025-08-07 20:00</t>
+          <t>2012-01-02 02:00 to 2021-01-01 05:00 | 2021-01-15 16:00 to 2025-08-08 07:00</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00</t>
+          <t>2012-01-02 04:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2025-08-08 05:00</t>
+          <t>2025-08-08 16:00</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2019-01-13 15:00 to 2019-01-20 17:00 (7.08 days) | 2020-12-31 18:00 to 2021-01-14 09:00 (13.62 days) | 2021-05-31 21:00 to 2021-06-10 10:00 (9.54 days) | 2021-06-14 23:00 to 2021-06-24 02:00 (9.12 days) | 2023-03-20 07:00 to 2023-03-27 17:00 (7.42 days) | 2023-08-21 19:00 to 2023-08-28 21:00 (7.08 days)</t>
+          <t>2019-01-14 02:00 to 2019-01-21 04:00 (7.08 days) | 2021-01-01 05:00 to 2021-01-14 20:00 (13.62 days) | 2021-06-01 08:00 to 2021-06-10 21:00 (9.54 days) | 2021-06-15 10:00 to 2021-06-24 13:00 (9.12 days) | 2023-03-20 18:00 to 2023-03-28 04:00 (7.42 days) | 2023-08-22 06:00 to 2023-08-29 08:00 (7.08 days)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00 to 2019-01-13 15:00 | 2019-01-20 17:00 to 2020-12-31 18:00 | 2021-01-14 09:00 to 2021-05-31 21:00 | 2021-06-10 10:00 to 2021-06-14 23:00 | 2021-06-24 02:00 to 2023-03-20 07:00 | 2023-03-27 17:00 to 2023-08-21 19:00 | 2023-08-28 21:00 to 2025-08-08 05:00</t>
+          <t>2012-01-02 04:00 to 2019-01-14 02:00 | 2019-01-21 04:00 to 2021-01-01 05:00 | 2021-01-14 20:00 to 2021-06-01 08:00 | 2021-06-10 21:00 to 2021-06-15 10:00 | 2021-06-24 13:00 to 2023-03-20 18:00 | 2023-03-28 04:00 to 2023-08-22 06:00 | 2023-08-29 08:00 to 2025-08-08 16:00</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2012-01-01 14:00</t>
+          <t>2012-01-02 01:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2025-08-04 05:00</t>
+          <t>2025-08-04 16:00</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2019-05-08 21:00 to 2019-05-17 04:00 (8.29 days) | 2020-12-28 22:00 to 2021-01-14 10:00 (16.50 days)</t>
+          <t>2019-05-09 08:00 to 2019-05-17 15:00 (8.29 days) | 2020-12-29 09:00 to 2021-01-14 21:00 (16.50 days)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2012-01-01 14:00 to 2019-05-08 21:00 | 2019-05-17 04:00 to 2020-12-28 22:00 | 2021-01-14 10:00 to 2025-08-04 05:00</t>
+          <t>2012-01-02 01:00 to 2019-05-09 08:00 | 2019-05-17 15:00 to 2020-12-29 09:00 | 2021-01-14 21:00 to 2025-08-04 16:00</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2012-01-01 08:00</t>
+          <t>2012-01-01 19:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2025-08-07 22:00</t>
+          <t>2025-08-08 09:00</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2020-12-31 18:00 to 2021-01-14 09:00 (13.62 days)</t>
+          <t>2021-01-01 05:00 to 2021-01-14 20:00 (13.62 days)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2012-01-01 08:00 to 2020-12-31 18:00 | 2021-01-14 09:00 to 2025-08-07 22:00</t>
+          <t>2012-01-01 19:00 to 2021-01-01 05:00 | 2021-01-14 20:00 to 2025-08-08 09:00</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2012-06-06 05:00</t>
+          <t>2012-06-06 16:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2025-08-08 06:00</t>
+          <t>2025-08-08 17:00</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2020-06-17 02:00 to 2020-06-26 14:00 (9.50 days) | 2020-12-29 00:00 to 2021-01-14 12:00 (16.50 days)</t>
+          <t>2020-06-17 13:00 to 2020-06-27 01:00 (9.50 days) | 2020-12-29 11:00 to 2021-01-14 23:00 (16.50 days)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2012-06-06 05:00 to 2020-06-17 02:00 | 2020-06-26 14:00 to 2020-12-29 00:00 | 2021-01-14 12:00 to 2025-08-08 06:00</t>
+          <t>2012-06-06 16:00 to 2020-06-17 13:00 | 2020-06-27 01:00 to 2020-12-29 11:00 | 2021-01-14 23:00 to 2025-08-08 17:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00</t>
+          <t>2012-01-02 04:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2025-08-08 04:00</t>
+          <t>2025-08-08 15:00</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3896,12 +3896,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2020-04-19 23:00 to 2020-09-25 05:00 (158.25 days) | 2020-12-28 16:00 to 2021-01-14 16:00 (17.00 days) | 2023-12-31 07:00 to 2025-02-05 12:00 (402.21 days)</t>
+          <t>2020-04-20 10:00 to 2020-09-25 16:00 (158.25 days) | 2020-12-29 03:00 to 2021-01-15 03:00 (17.00 days) | 2023-12-31 18:00 to 2025-02-05 23:00 (402.21 days)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00 to 2020-04-19 23:00 | 2020-09-25 05:00 to 2020-12-28 16:00 | 2021-01-14 16:00 to 2023-12-31 07:00 | 2025-02-05 12:00 to 2025-08-08 04:00</t>
+          <t>2012-01-02 04:00 to 2020-04-20 10:00 | 2020-09-25 16:00 to 2020-12-29 03:00 | 2021-01-15 03:00 to 2023-12-31 18:00 | 2025-02-05 23:00 to 2025-08-08 15:00</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00</t>
+          <t>2012-01-02 04:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2025-08-08 05:00</t>
+          <t>2025-08-08 16:00</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2020-12-28 17:00 to 2021-01-14 17:00 (17.00 days) | 2021-06-09 19:00 to 2021-06-18 09:00 (8.58 days) | 2023-06-28 05:00 to 2023-07-06 22:00 (8.71 days)</t>
+          <t>2020-12-29 04:00 to 2021-01-15 04:00 (17.00 days) | 2021-06-10 06:00 to 2021-06-18 20:00 (8.58 days) | 2023-06-28 16:00 to 2023-07-07 09:00 (8.71 days)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00 to 2020-12-28 17:00 | 2021-01-14 17:00 to 2021-06-09 19:00 | 2021-06-18 09:00 to 2023-06-28 05:00 | 2023-07-06 22:00 to 2025-08-08 05:00</t>
+          <t>2012-01-02 04:00 to 2020-12-29 04:00 | 2021-01-15 04:00 to 2021-06-10 06:00 | 2021-06-18 20:00 to 2023-06-28 16:00 | 2023-07-07 09:00 to 2025-08-08 16:00</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2012-01-01 09:00</t>
+          <t>2012-01-01 20:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2025-08-08 06:00</t>
+          <t>2025-08-08 17:00</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2019-02-02 09:00 to 2019-03-23 06:00 (48.83 days) | 2020-12-28 16:00 to 2021-01-14 16:00 (17.00 days)</t>
+          <t>2019-02-02 20:00 to 2019-03-23 17:00 (48.83 days) | 2020-12-29 03:00 to 2021-01-15 03:00 (17.00 days)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2012-01-01 09:00 to 2019-02-02 09:00 | 2019-03-23 06:00 to 2020-12-28 16:00 | 2021-01-14 16:00 to 2025-08-08 06:00</t>
+          <t>2012-01-01 20:00 to 2019-02-02 20:00 | 2019-03-23 17:00 to 2020-12-29 03:00 | 2021-01-15 03:00 to 2025-08-08 17:00</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2014-10-03 09:00</t>
+          <t>2014-10-03 20:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2025-08-08 04:00</t>
+          <t>2025-08-08 15:00</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2014-10-03 10:00 to 2015-06-30 19:00 (270.38 days) | 2015-06-30 19:00 to 2015-07-21 09:00 (20.58 days)</t>
+          <t>2014-10-03 21:00 to 2015-07-01 06:00 (270.38 days) | 2015-07-01 06:00 to 2015-07-21 20:00 (20.58 days)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2014-10-03 09:00 to 2014-10-03 10:00 | 2015-06-30 19:00 to 2015-06-30 19:00 | 2015-07-21 09:00 to 2025-08-08 04:00</t>
+          <t>2014-10-03 20:00 to 2014-10-03 21:00 | 2015-07-01 06:00 to 2015-07-01 06:00 | 2015-07-21 20:00 to 2025-08-08 15:00</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2014-10-30 10:00</t>
+          <t>2014-10-30 21:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2025-08-08 05:00</t>
+          <t>2025-08-08 16:00</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2020-12-28 18:00 to 2021-01-14 18:00 (17.00 days)</t>
+          <t>2020-12-29 05:00 to 2021-01-15 05:00 (17.00 days)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2014-10-30 10:00 to 2020-12-28 18:00 | 2021-01-14 18:00 to 2025-08-08 05:00</t>
+          <t>2014-10-30 21:00 to 2020-12-29 05:00 | 2021-01-15 05:00 to 2025-08-08 16:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2016-03-21 18:00</t>
+          <t>2016-03-22 05:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2023-12-31 06:00</t>
+          <t>2023-12-31 17:00</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -4123,7 +4123,7 @@
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2016-03-21 18:00 to 2023-12-31 06:00</t>
+          <t>2016-03-22 05:00 to 2023-12-31 17:00</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2012-01-01 08:00</t>
+          <t>2012-01-01 19:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2025-08-08 04:00</t>
+          <t>2025-08-08 15:00</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2013-04-23 10:00 to 2013-05-09 05:00 (15.79 days)</t>
+          <t>2013-04-23 21:00 to 2013-05-09 16:00 (15.79 days)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2012-01-01 08:00 to 2013-04-23 10:00 | 2013-05-09 05:00 to 2025-08-08 04:00</t>
+          <t>2012-01-01 19:00 to 2013-04-23 21:00 | 2013-05-09 16:00 to 2025-08-08 15:00</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2012-01-01 19:00</t>
+          <t>2012-01-02 06:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2022-03-22 12:00 to 2022-03-30 09:00 (7.88 days) | 2024-11-24 16:00 to 2024-12-06 08:00 (11.67 days)</t>
+          <t>2022-03-22 23:00 to 2022-03-30 20:00 (7.88 days) | 2024-11-25 03:00 to 2024-12-06 19:00 (11.67 days)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2012-01-01 19:00 to 2022-03-22 12:00 | 2022-03-30 09:00 to 2024-11-24 16:00 | 2024-12-06 08:00 to 2025-08-08 02:00</t>
+          <t>2012-01-02 06:00 to 2022-03-22 23:00 | 2022-03-30 20:00 to 2024-11-25 03:00 | 2024-12-06 19:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2012-01-01 15:00</t>
+          <t>2012-01-02 02:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2025-08-07 20:00</t>
+          <t>2025-08-08 07:00</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2022-05-29 21:00 to 2022-06-08 08:00 (9.46 days)</t>
+          <t>2022-05-30 08:00 to 2022-06-08 19:00 (9.46 days)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2012-01-01 15:00 to 2022-05-29 21:00 | 2022-06-08 08:00 to 2025-08-07 20:00</t>
+          <t>2012-01-02 02:00 to 2022-05-30 08:00 | 2022-06-08 19:00 to 2025-08-08 07:00</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2014-08-01 10:00</t>
+          <t>2014-08-01 21:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2025-08-07 19:00</t>
+          <t>2025-08-08 06:00</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -4299,7 +4299,7 @@
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2014-08-01 10:00 to 2025-08-07 19:00</t>
+          <t>2014-08-01 21:00 to 2025-08-08 06:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2016-09-12 09:00</t>
+          <t>2016-09-12 20:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2025-08-08 02:00</t>
+          <t>2025-08-08 13:00</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -4337,7 +4337,7 @@
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2016-09-12 09:00 to 2025-08-08 02:00</t>
+          <t>2016-09-12 20:00 to 2025-08-08 13:00</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2022-11-04 09:00</t>
+          <t>2022-11-04 20:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2025-08-08 06:00</t>
+          <t>2025-08-08 17:00</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -4375,7 +4375,7 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2022-11-04 09:00 to 2025-08-08 06:00</t>
+          <t>2022-11-04 20:00 to 2025-08-08 17:00</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2019-07-16 09:00</t>
+          <t>2019-07-16 20:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2025-08-07 21:00</t>
+          <t>2025-08-08 08:00</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -4413,7 +4413,7 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2019-07-16 09:00 to 2025-08-07 21:00</t>
+          <t>2019-07-16 20:00 to 2025-08-08 08:00</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2023-08-22 16:00</t>
+          <t>2023-08-23 03:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2025-08-07 21:00</t>
+          <t>2025-08-08 08:00</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2024-08-28 09:00 to 2024-09-06 16:00 (9.29 days)</t>
+          <t>2024-08-28 20:00 to 2024-09-07 03:00 (9.29 days)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2023-08-22 16:00 to 2024-08-28 09:00 | 2024-09-06 16:00 to 2025-08-07 21:00</t>
+          <t>2023-08-23 03:00 to 2024-08-28 20:00 | 2024-09-07 03:00 to 2025-08-08 08:00</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2021-07-28 06:00</t>
+          <t>2021-07-28 17:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2025-08-07 19:00</t>
+          <t>2025-08-08 06:00</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2021-07-28 06:00 to 2021-08-07 22:00 (10.67 days) | 2021-08-25 10:00 to 2021-09-03 01:00 (8.62 days) | 2021-09-14 22:00 to 2021-10-14 20:00 (29.92 days) | 2022-01-12 09:00 to 2022-04-12 11:00 (90.04 days) | 2022-12-22 05:00 to 2023-05-24 07:00 (153.04 days) | 2023-12-17 15:00 to 2024-06-25 08:00 (190.67 days) | 2024-12-30 07:00 to 2025-03-15 09:00 (75.04 days)</t>
+          <t>2021-07-28 17:00 to 2021-08-08 09:00 (10.67 days) | 2021-08-25 21:00 to 2021-09-03 12:00 (8.62 days) | 2021-09-15 09:00 to 2021-10-15 07:00 (29.92 days) | 2022-01-12 20:00 to 2022-04-12 22:00 (90.04 days) | 2022-12-22 16:00 to 2023-05-24 18:00 (153.04 days) | 2023-12-18 02:00 to 2024-06-25 19:00 (190.67 days) | 2024-12-30 18:00 to 2025-03-15 20:00 (75.04 days)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2021-07-28 06:00 to 2021-07-28 06:00 | 2021-08-07 22:00 to 2021-08-25 10:00 | 2021-09-03 01:00 to 2021-09-14 22:00 | 2021-10-14 20:00 to 2022-01-12 09:00 | 2022-04-12 11:00 to 2022-12-22 05:00 | 2023-05-24 07:00 to 2023-12-17 15:00 | 2024-06-25 08:00 to 2024-12-30 07:00 | 2025-03-15 09:00 to 2025-08-07 19:00</t>
+          <t>2021-07-28 17:00 to 2021-07-28 17:00 | 2021-08-08 09:00 to 2021-08-25 21:00 | 2021-09-03 12:00 to 2021-09-15 09:00 | 2021-10-15 07:00 to 2022-01-12 20:00 | 2022-04-12 22:00 to 2022-12-22 16:00 | 2023-05-24 18:00 to 2023-12-18 02:00 | 2024-06-25 19:00 to 2024-12-30 18:00 | 2025-03-15 20:00 to 2025-08-08 06:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2012-01-01 09:00</t>
+          <t>2012-01-01 20:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2025-08-08 06:00</t>
+          <t>2025-08-08 17:00</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2024-09-19 05:00 to 2024-10-07 06:00 (18.04 days)</t>
+          <t>2024-09-19 16:00 to 2024-10-07 17:00 (18.04 days)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2012-01-01 09:00 to 2024-09-19 05:00 | 2024-10-07 06:00 to 2025-08-08 06:00</t>
+          <t>2012-01-01 20:00 to 2024-09-19 16:00 | 2024-10-07 17:00 to 2025-08-08 17:00</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2012-01-01 08:00</t>
+          <t>2012-01-01 19:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2025-08-08 06:00</t>
+          <t>2025-08-08 17:00</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -4592,12 +4592,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2013-08-27 16:00 to 2015-02-18 09:00 (539.75 days) | 2015-02-18 09:00 to 2018-10-02 19:00 (1322.38 days) | 2024-05-23 07:00 to 2024-06-25 04:00 (32.88 days) | 2025-01-18 05:00 to 2025-01-25 17:00 (7.50 days) | 2025-02-14 17:00 to 2025-02-23 05:00 (8.50 days)</t>
+          <t>2013-08-28 03:00 to 2015-02-18 20:00 (539.75 days) | 2015-02-18 20:00 to 2018-10-03 06:00 (1322.38 days) | 2024-05-23 18:00 to 2024-06-25 15:00 (32.88 days) | 2025-01-18 16:00 to 2025-01-26 04:00 (7.50 days) | 2025-02-15 04:00 to 2025-02-23 16:00 (8.50 days)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2012-01-01 08:00 to 2013-08-27 16:00 | 2015-02-18 09:00 to 2015-02-18 09:00 | 2018-10-02 19:00 to 2024-05-23 07:00 | 2024-06-25 04:00 to 2025-01-18 05:00 | 2025-01-25 17:00 to 2025-02-14 17:00 | 2025-02-23 05:00 to 2025-08-08 06:00</t>
+          <t>2012-01-01 19:00 to 2013-08-28 03:00 | 2015-02-18 20:00 to 2015-02-18 20:00 | 2018-10-03 06:00 to 2024-05-23 18:00 | 2024-06-25 15:00 to 2025-01-18 16:00 | 2025-01-26 04:00 to 2025-02-15 04:00 | 2025-02-23 16:00 to 2025-08-08 17:00</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00</t>
+          <t>2012-01-02 03:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2025-08-08 00:00</t>
+          <t>2025-08-08 11:00</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2019-01-08 07:00 to 2019-01-16 08:00 (8.04 days) | 2019-01-17 06:00 to 2019-01-28 08:00 (11.08 days) | 2019-02-08 08:00 to 2019-02-18 06:00 (9.92 days)</t>
+          <t>2019-01-08 18:00 to 2019-01-16 19:00 (8.04 days) | 2019-01-17 17:00 to 2019-01-28 19:00 (11.08 days) | 2019-02-08 19:00 to 2019-02-18 17:00 (9.92 days)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00 to 2019-01-08 07:00 | 2019-01-16 08:00 to 2019-01-17 06:00 | 2019-01-28 08:00 to 2019-02-08 08:00 | 2019-02-18 06:00 to 2025-08-08 00:00</t>
+          <t>2012-01-02 03:00 to 2019-01-08 18:00 | 2019-01-16 19:00 to 2019-01-17 17:00 | 2019-01-28 19:00 to 2019-02-08 19:00 | 2019-02-18 17:00 to 2025-08-08 11:00</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00</t>
+          <t>2012-01-02 04:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2025-08-07 19:00</t>
+          <t>2025-08-08 06:00</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2012-02-06 15:00 to 2012-02-15 03:00 (8.50 days) | 2022-11-30 05:00 to 2022-12-08 17:00 (8.50 days) | 2025-02-03 17:00 to 2025-02-15 17:00 (12.00 days)</t>
+          <t>2012-02-07 02:00 to 2012-02-15 14:00 (8.50 days) | 2022-11-30 16:00 to 2022-12-09 04:00 (8.50 days) | 2025-02-04 04:00 to 2025-02-16 04:00 (12.00 days)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00 to 2012-02-06 15:00 | 2012-02-15 03:00 to 2022-11-30 05:00 | 2022-12-08 17:00 to 2025-02-03 17:00 | 2025-02-15 17:00 to 2025-08-07 19:00</t>
+          <t>2012-01-02 04:00 to 2012-02-07 02:00 | 2012-02-15 14:00 to 2022-11-30 16:00 | 2022-12-09 04:00 to 2025-02-04 04:00 | 2025-02-16 04:00 to 2025-08-08 06:00</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2012-04-18 22:00</t>
+          <t>2012-04-19 09:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2025-07-24 11:00</t>
+          <t>2025-07-24 22:00</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2019-09-10 19:00 to 2019-09-28 03:00 (17.33 days) | 2019-09-28 03:00 to 2019-10-29 04:00 (31.04 days) | 2020-06-19 16:00 to 2020-08-27 10:00 (68.75 days) | 2022-01-10 23:00 to 2022-02-10 04:00 (30.21 days) | 2022-02-11 04:00 to 2022-04-23 10:00 (71.21 days) | 2022-04-24 22:00 to 2022-06-08 07:00 (44.38 days)</t>
+          <t>2019-09-11 06:00 to 2019-09-28 14:00 (17.33 days) | 2019-09-28 14:00 to 2019-10-29 15:00 (31.04 days) | 2020-06-20 03:00 to 2020-08-27 21:00 (68.75 days) | 2022-01-11 10:00 to 2022-02-10 15:00 (30.21 days) | 2022-02-11 15:00 to 2022-04-23 21:00 (71.21 days) | 2022-04-25 09:00 to 2022-06-08 18:00 (44.38 days)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2012-04-18 22:00 to 2019-09-10 19:00 | 2019-09-28 03:00 to 2019-09-28 03:00 | 2019-10-29 04:00 to 2020-06-19 16:00 | 2020-08-27 10:00 to 2022-01-10 23:00 | 2022-02-10 04:00 to 2022-02-11 04:00 | 2022-04-23 10:00 to 2022-04-24 22:00 | 2022-06-08 07:00 to 2025-07-24 11:00</t>
+          <t>2012-04-19 09:00 to 2019-09-11 06:00 | 2019-09-28 14:00 to 2019-09-28 14:00 | 2019-10-29 15:00 to 2020-06-20 03:00 | 2020-08-27 21:00 to 2022-01-11 10:00 | 2022-02-10 15:00 to 2022-02-11 15:00 | 2022-04-23 21:00 to 2022-04-25 09:00 | 2022-06-08 18:00 to 2025-07-24 22:00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2012-01-01 15:00</t>
+          <t>2012-01-02 02:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2025-08-07 20:00</t>
+          <t>2025-08-08 07:00</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2020-06-19 16:00 to 2020-09-25 09:00 (97.71 days) | 2020-12-26 17:00 to 2021-01-05 05:00 (9.50 days)</t>
+          <t>2020-06-20 03:00 to 2020-09-25 20:00 (97.71 days) | 2020-12-27 04:00 to 2021-01-05 16:00 (9.50 days)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2012-01-01 15:00 to 2020-06-19 16:00 | 2020-09-25 09:00 to 2020-12-26 17:00 | 2021-01-05 05:00 to 2025-08-07 20:00</t>
+          <t>2012-01-02 02:00 to 2020-06-20 03:00 | 2020-09-25 20:00 to 2020-12-27 04:00 | 2021-01-05 16:00 to 2025-08-08 07:00</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2012-01-01 13:00</t>
+          <t>2012-01-02 00:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2025-08-07 21:00</t>
+          <t>2025-08-08 08:00</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2013-06-30 06:00 to 2013-07-10 05:00 (9.96 days) | 2015-12-13 20:00 to 2015-12-30 16:00 (16.83 days) | 2016-12-25 16:00 to 2017-01-03 06:00 (8.58 days)</t>
+          <t>2013-06-30 17:00 to 2013-07-10 16:00 (9.96 days) | 2015-12-14 07:00 to 2015-12-31 03:00 (16.83 days) | 2016-12-26 03:00 to 2017-01-03 17:00 (8.58 days)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2012-01-01 13:00 to 2013-06-30 06:00 | 2013-07-10 05:00 to 2015-12-13 20:00 | 2015-12-30 16:00 to 2016-12-25 16:00 | 2017-01-03 06:00 to 2025-08-07 21:00</t>
+          <t>2012-01-02 00:00 to 2013-06-30 17:00 | 2013-07-10 16:00 to 2015-12-14 07:00 | 2015-12-31 03:00 to 2016-12-26 03:00 | 2017-01-03 17:00 to 2025-08-08 08:00</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2014-12-31 19:00</t>
+          <t>2015-01-01 06:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2025-08-07 22:00</t>
+          <t>2025-08-08 09:00</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -4865,7 +4865,7 @@
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2014-12-31 19:00 to 2025-08-07 22:00</t>
+          <t>2015-01-01 06:00 to 2025-08-08 09:00</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -4882,12 +4882,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2012-01-01 11:00</t>
+          <t>2012-01-01 22:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2025-08-07 23:00</t>
+          <t>2025-08-08 10:00</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -4906,12 +4906,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2014-11-10 23:00 to 2015-01-28 07:00 (78.33 days)</t>
+          <t>2014-11-11 10:00 to 2015-01-28 18:00 (78.33 days)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2012-01-01 11:00 to 2014-11-10 23:00 | 2015-01-28 07:00 to 2025-08-07 23:00</t>
+          <t>2012-01-01 22:00 to 2014-11-11 10:00 | 2015-01-28 18:00 to 2025-08-08 10:00</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2012-01-01 13:00</t>
+          <t>2012-01-02 00:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2025-08-08 04:00</t>
+          <t>2025-08-08 15:00</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -4949,7 +4949,7 @@
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2012-01-01 13:00 to 2025-08-08 04:00</t>
+          <t>2012-01-02 00:00 to 2025-08-08 15:00</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2012-01-01 13:00</t>
+          <t>2012-01-02 00:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2025-08-07 23:00</t>
+          <t>2025-08-08 10:00</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4987,7 +4987,7 @@
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2012-01-01 13:00 to 2025-08-07 23:00</t>
+          <t>2012-01-02 00:00 to 2025-08-08 10:00</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2012-01-01 15:00</t>
+          <t>2012-01-02 02:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2025-08-07 19:00</t>
+          <t>2025-08-08 06:00</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -5025,7 +5025,7 @@
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2012-01-01 15:00 to 2025-08-07 19:00</t>
+          <t>2012-01-02 02:00 to 2025-08-08 06:00</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -5042,12 +5042,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2012-01-01 08:00</t>
+          <t>2012-01-01 19:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2025-08-07 23:00</t>
+          <t>2025-08-08 10:00</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2012-04-27 12:00 to 2012-05-11 04:00 (13.67 days) | 2017-12-09 16:00 to 2017-12-18 08:00 (8.67 days)</t>
+          <t>2012-04-27 23:00 to 2012-05-11 15:00 (13.67 days) | 2017-12-10 03:00 to 2017-12-18 19:00 (8.67 days)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2012-01-01 08:00 to 2012-04-27 12:00 | 2012-05-11 04:00 to 2017-12-09 16:00 | 2017-12-18 08:00 to 2025-08-07 23:00</t>
+          <t>2012-01-01 19:00 to 2012-04-27 23:00 | 2012-05-11 15:00 to 2017-12-10 03:00 | 2017-12-18 19:00 to 2025-08-08 10:00</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2012-01-01 14:00</t>
+          <t>2012-01-02 01:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2025-08-07 19:00</t>
+          <t>2025-08-08 06:00</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2013-03-04 19:00 to 2014-04-01 10:00 (392.58 days)</t>
+          <t>2013-03-05 06:00 to 2014-04-01 21:00 (392.58 days)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2012-01-01 14:00 to 2013-03-04 19:00 | 2014-04-01 10:00 to 2025-08-07 19:00</t>
+          <t>2012-01-02 01:00 to 2013-03-05 06:00 | 2014-04-01 21:00 to 2025-08-08 06:00</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2012-01-01 13:00</t>
+          <t>2012-01-02 00:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2025-08-07 23:00</t>
+          <t>2025-08-08 10:00</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2019-12-28 17:00 to 2020-01-09 05:00 (11.50 days) | 2020-01-10 08:00 to 2020-01-20 17:00 (10.38 days) | 2020-01-23 11:00 to 2020-02-02 17:00 (10.25 days)</t>
+          <t>2019-12-29 04:00 to 2020-01-09 16:00 (11.50 days) | 2020-01-10 19:00 to 2020-01-21 04:00 (10.38 days) | 2020-01-23 22:00 to 2020-02-03 04:00 (10.25 days)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2012-01-01 13:00 to 2019-12-28 17:00 | 2020-01-09 05:00 to 2020-01-10 08:00 | 2020-01-20 17:00 to 2020-01-23 11:00 | 2020-02-02 17:00 to 2025-08-07 23:00</t>
+          <t>2012-01-02 00:00 to 2019-12-29 04:00 | 2020-01-09 16:00 to 2020-01-10 19:00 | 2020-01-21 04:00 to 2020-01-23 22:00 | 2020-02-03 04:00 to 2025-08-08 10:00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00</t>
+          <t>2012-01-02 04:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2025-08-07 19:00</t>
+          <t>2025-08-08 06:00</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2024-09-18 22:00 to 2024-09-30 09:00 (11.46 days)</t>
+          <t>2024-09-19 09:00 to 2024-09-30 20:00 (11.46 days)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00 to 2024-09-18 22:00 | 2024-09-30 09:00 to 2025-08-07 19:00</t>
+          <t>2012-01-02 04:00 to 2024-09-19 09:00 | 2024-09-30 20:00 to 2025-08-08 06:00</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2012-01-01 12:00</t>
+          <t>2012-01-01 23:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2025-08-08 04:00</t>
+          <t>2025-08-08 15:00</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2024-09-21 06:00 to 2024-10-21 05:00 (29.96 days) | 2025-02-11 19:00 to 2025-02-21 06:00 (9.46 days) | 2025-02-21 06:00 to 2025-03-04 03:00 (10.88 days)</t>
+          <t>2024-09-21 17:00 to 2024-10-21 16:00 (29.96 days) | 2025-02-12 06:00 to 2025-02-21 17:00 (9.46 days) | 2025-02-21 17:00 to 2025-03-04 14:00 (10.88 days)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2012-01-01 12:00 to 2024-09-21 06:00 | 2024-10-21 05:00 to 2025-02-11 19:00 | 2025-02-21 06:00 to 2025-02-21 06:00 | 2025-03-04 03:00 to 2025-08-08 04:00</t>
+          <t>2012-01-01 23:00 to 2024-09-21 17:00 | 2024-10-21 16:00 to 2025-02-12 06:00 | 2025-02-21 17:00 to 2025-02-21 17:00 | 2025-03-04 14:00 to 2025-08-08 15:00</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2012-01-01 12:00</t>
+          <t>2012-01-01 23:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2025-08-08 05:00</t>
+          <t>2025-08-08 16:00</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2019-04-06 19:00 to 2019-04-15 01:00 (8.25 days) | 2019-12-06 07:00 to 2019-12-21 05:00 (14.92 days) | 2024-09-21 06:00 to 2024-09-30 02:00 (8.83 days)</t>
+          <t>2019-04-07 06:00 to 2019-04-15 12:00 (8.25 days) | 2019-12-06 18:00 to 2019-12-21 16:00 (14.92 days) | 2024-09-21 17:00 to 2024-09-30 13:00 (8.83 days)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2012-01-01 12:00 to 2019-04-06 19:00 | 2019-04-15 01:00 to 2019-12-06 07:00 | 2019-12-21 05:00 to 2024-09-21 06:00 | 2024-09-30 02:00 to 2025-08-08 05:00</t>
+          <t>2012-01-01 23:00 to 2019-04-07 06:00 | 2019-04-15 12:00 to 2019-12-06 18:00 | 2019-12-21 16:00 to 2024-09-21 17:00 | 2024-09-30 13:00 to 2025-08-08 16:00</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2012-01-01 08:00</t>
+          <t>2012-01-01 19:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2025-08-07 21:00</t>
+          <t>2025-08-08 08:00</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2014-12-27 03:00 to 2015-01-14 06:00 (18.12 days) | 2024-09-21 06:00 to 2024-09-30 09:00 (9.12 days) | 2024-09-30 09:00 to 2024-10-21 05:00 (20.83 days) | 2025-02-24 19:00 to 2025-03-04 14:00 (7.79 days)</t>
+          <t>2014-12-27 14:00 to 2015-01-14 17:00 (18.12 days) | 2024-09-21 17:00 to 2024-09-30 20:00 (9.12 days) | 2024-09-30 20:00 to 2024-10-21 16:00 (20.83 days) | 2025-02-25 06:00 to 2025-03-05 01:00 (7.79 days)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2012-01-01 08:00 to 2014-12-27 03:00 | 2015-01-14 06:00 to 2024-09-21 06:00 | 2024-09-30 09:00 to 2024-09-30 09:00 | 2024-10-21 05:00 to 2025-02-24 19:00 | 2025-03-04 14:00 to 2025-08-07 21:00</t>
+          <t>2012-01-01 19:00 to 2014-12-27 14:00 | 2015-01-14 17:00 to 2024-09-21 17:00 | 2024-09-30 20:00 to 2024-09-30 20:00 | 2024-10-21 16:00 to 2025-02-25 06:00 | 2025-03-05 01:00 to 2025-08-08 08:00</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2012-01-01 10:00</t>
+          <t>2012-01-01 21:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2025-06-17 17:00</t>
+          <t>2025-06-18 04:00</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -5388,12 +5388,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2017-07-27 05:00 to 2017-08-05 04:00 (8.96 days) | 2023-01-10 10:00 to 2023-01-18 13:00 (8.12 days) | 2023-01-18 13:00 to 2023-01-28 19:00 (10.25 days) | 2023-01-28 19:00 to 2023-02-09 02:00 (11.29 days) | 2023-02-09 02:00 to 2023-02-19 19:00 (10.71 days) | 2023-02-26 19:00 to 2023-03-08 19:00 (10.00 days) | 2023-03-16 10:00 to 2023-03-24 14:00 (8.17 days) | 2023-03-30 08:00 to 2023-05-03 20:00 (34.50 days) | 2023-05-03 20:00 to 2023-05-21 20:00 (18.00 days) | 2023-06-05 21:00 to 2023-09-15 03:00 (101.25 days) | 2024-06-26 11:00 to 2024-07-03 21:00 (7.42 days) | 2024-07-07 07:00 to 2024-08-02 09:00 (26.08 days) | 2024-09-21 22:00 to 2024-10-01 22:00 (10.00 days) | 2024-12-13 04:00 to 2024-12-20 17:00 (7.54 days) | 2024-12-20 17:00 to 2025-02-05 04:00 (46.46 days)</t>
+          <t>2017-07-27 16:00 to 2017-08-05 15:00 (8.96 days) | 2023-01-10 21:00 to 2023-01-19 00:00 (8.12 days) | 2023-01-19 00:00 to 2023-01-29 06:00 (10.25 days) | 2023-01-29 06:00 to 2023-02-09 13:00 (11.29 days) | 2023-02-09 13:00 to 2023-02-20 06:00 (10.71 days) | 2023-02-27 06:00 to 2023-03-09 06:00 (10.00 days) | 2023-03-16 21:00 to 2023-03-25 01:00 (8.17 days) | 2023-03-30 19:00 to 2023-05-04 07:00 (34.50 days) | 2023-05-04 07:00 to 2023-05-22 07:00 (18.00 days) | 2023-06-06 08:00 to 2023-09-15 14:00 (101.25 days) | 2024-06-26 22:00 to 2024-07-04 08:00 (7.42 days) | 2024-07-07 18:00 to 2024-08-02 20:00 (26.08 days) | 2024-09-22 09:00 to 2024-10-02 09:00 (10.00 days) | 2024-12-13 15:00 to 2024-12-21 04:00 (7.54 days) | 2024-12-21 04:00 to 2025-02-05 15:00 (46.46 days)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2012-01-01 10:00 to 2017-07-27 05:00 | 2017-08-05 04:00 to 2023-01-10 10:00 | 2023-01-18 13:00 to 2023-01-18 13:00 | 2023-01-28 19:00 to 2023-01-28 19:00 | 2023-02-09 02:00 to 2023-02-09 02:00 | 2023-02-19 19:00 to 2023-02-26 19:00 | 2023-03-08 19:00 to 2023-03-16 10:00 | 2023-03-24 14:00 to 2023-03-30 08:00 | 2023-05-03 20:00 to 2023-05-03 20:00 | 2023-05-21 20:00 to 2023-06-05 21:00 | 2023-09-15 03:00 to 2024-06-26 11:00 | 2024-07-03 21:00 to 2024-07-07 07:00 | 2024-08-02 09:00 to 2024-09-21 22:00 | 2024-10-01 22:00 to 2024-12-13 04:00 | 2024-12-20 17:00 to 2024-12-20 17:00 | 2025-02-05 04:00 to 2025-06-17 17:00</t>
+          <t>2012-01-01 21:00 to 2017-07-27 16:00 | 2017-08-05 15:00 to 2023-01-10 21:00 | 2023-01-19 00:00 to 2023-01-19 00:00 | 2023-01-29 06:00 to 2023-01-29 06:00 | 2023-02-09 13:00 to 2023-02-09 13:00 | 2023-02-20 06:00 to 2023-02-27 06:00 | 2023-03-09 06:00 to 2023-03-16 21:00 | 2023-03-25 01:00 to 2023-03-30 19:00 | 2023-05-04 07:00 to 2023-05-04 07:00 | 2023-05-22 07:00 to 2023-06-06 08:00 | 2023-09-15 14:00 to 2024-06-26 22:00 | 2024-07-04 08:00 to 2024-07-07 18:00 | 2024-08-02 20:00 to 2024-09-22 09:00 | 2024-10-02 09:00 to 2024-12-13 15:00 | 2024-12-21 04:00 to 2024-12-21 04:00 | 2025-02-05 15:00 to 2025-06-18 04:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00</t>
+          <t>2012-01-02 03:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2025-08-07 20:00</t>
+          <t>2025-08-08 07:00</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2024-02-25 05:00 to 2024-03-04 02:00 (7.88 days)</t>
+          <t>2024-02-25 16:00 to 2024-03-04 13:00 (7.88 days)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2012-01-01 16:00 to 2024-02-25 05:00 | 2024-03-04 02:00 to 2025-08-07 20:00</t>
+          <t>2012-01-02 03:00 to 2024-02-25 16:00 | 2024-03-04 13:00 to 2025-08-08 07:00</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -5456,12 +5456,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00</t>
+          <t>2012-01-02 04:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2025-08-08 06:00</t>
+          <t>2025-08-08 17:00</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2024-09-17 23:00 to 2024-09-30 06:00 (12.29 days) | 2024-09-30 06:00 to 2024-10-15 06:00 (15.00 days) | 2025-02-11 19:00 to 2025-03-04 08:00 (20.54 days)</t>
+          <t>2024-09-18 10:00 to 2024-09-30 17:00 (12.29 days) | 2024-09-30 17:00 to 2024-10-15 17:00 (15.00 days) | 2025-02-12 06:00 to 2025-03-04 19:00 (20.54 days)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00 to 2024-09-17 23:00 | 2024-09-30 06:00 to 2024-09-30 06:00 | 2024-10-15 06:00 to 2025-02-11 19:00 | 2025-03-04 08:00 to 2025-08-08 06:00</t>
+          <t>2012-01-02 04:00 to 2024-09-18 10:00 | 2024-09-30 17:00 to 2024-09-30 17:00 | 2024-10-15 17:00 to 2025-02-12 06:00 | 2025-03-04 19:00 to 2025-08-08 17:00</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -5502,12 +5502,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2012-01-01 09:00</t>
+          <t>2012-01-01 20:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2025-08-08 01:00</t>
+          <t>2025-08-08 12:00</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2012-05-26 09:00 to 2012-06-10 21:00 (15.50 days) | 2012-06-12 02:00 to 2012-06-20 19:00 (8.71 days) | 2012-06-21 05:00 to 2012-07-08 20:00 (17.62 days) | 2012-12-28 01:00 to 2013-01-16 08:00 (19.29 days) | 2013-03-11 19:00 to 2013-03-20 06:00 (8.46 days) | 2013-03-26 19:00 to 2013-04-05 10:00 (9.62 days) | 2013-06-04 07:00 to 2013-07-29 04:00 (54.88 days) | 2017-04-11 21:00 to 2017-04-19 06:00 (7.38 days) | 2024-09-21 06:00 to 2024-10-01 17:00 (10.46 days)</t>
+          <t>2012-05-26 20:00 to 2012-06-11 08:00 (15.50 days) | 2012-06-12 13:00 to 2012-06-21 06:00 (8.71 days) | 2012-06-21 16:00 to 2012-07-09 07:00 (17.62 days) | 2012-12-28 12:00 to 2013-01-16 19:00 (19.29 days) | 2013-03-12 06:00 to 2013-03-20 17:00 (8.46 days) | 2013-03-27 06:00 to 2013-04-05 21:00 (9.62 days) | 2013-06-04 18:00 to 2013-07-29 15:00 (54.88 days) | 2017-04-12 08:00 to 2017-04-19 17:00 (7.38 days) | 2024-09-21 17:00 to 2024-10-02 04:00 (10.46 days)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2012-01-01 09:00 to 2012-05-26 09:00 | 2012-06-10 21:00 to 2012-06-12 02:00 | 2012-06-20 19:00 to 2012-06-21 05:00 | 2012-07-08 20:00 to 2012-12-28 01:00 | 2013-01-16 08:00 to 2013-03-11 19:00 | 2013-03-20 06:00 to 2013-03-26 19:00 | 2013-04-05 10:00 to 2013-06-04 07:00 | 2013-07-29 04:00 to 2017-04-11 21:00 | 2017-04-19 06:00 to 2024-09-21 06:00 | 2024-10-01 17:00 to 2025-08-08 01:00</t>
+          <t>2012-01-01 20:00 to 2012-05-26 20:00 | 2012-06-11 08:00 to 2012-06-12 13:00 | 2012-06-21 06:00 to 2012-06-21 16:00 | 2012-07-09 07:00 to 2012-12-28 12:00 | 2013-01-16 19:00 to 2013-03-12 06:00 | 2013-03-20 17:00 to 2013-03-27 06:00 | 2013-04-05 21:00 to 2013-06-04 18:00 | 2013-07-29 15:00 to 2017-04-12 08:00 | 2017-04-19 17:00 to 2024-09-21 17:00 | 2024-10-02 04:00 to 2025-08-08 12:00</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -5548,12 +5548,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2012-01-01 15:00</t>
+          <t>2012-01-02 02:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2023-12-31 01:00</t>
+          <t>2023-12-31 12:00</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2023-11-02 20:00 to 2023-11-20 04:00 (17.38 days)</t>
+          <t>2023-11-03 07:00 to 2023-11-20 15:00 (17.38 days)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2012-01-01 15:00 to 2023-11-02 20:00 | 2023-11-20 04:00 to 2023-12-31 01:00</t>
+          <t>2012-01-02 02:00 to 2023-11-03 07:00 | 2023-11-20 15:00 to 2023-12-31 12:00</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2012-01-01 19:00</t>
+          <t>2012-01-02 06:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2023-12-31 07:00</t>
+          <t>2023-12-31 18:00</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -5615,7 +5615,7 @@
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2012-01-01 19:00 to 2023-12-31 07:00</t>
+          <t>2012-01-02 06:00 to 2023-12-31 18:00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2012-01-01 11:00</t>
+          <t>2012-01-01 22:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2025-08-08 06:00</t>
+          <t>2025-08-08 17:00</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -5653,7 +5653,7 @@
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2012-01-01 11:00 to 2025-08-08 06:00</t>
+          <t>2012-01-01 22:00 to 2025-08-08 17:00</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2014-12-31 20:00</t>
+          <t>2015-01-01 07:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2025-08-08 01:00</t>
+          <t>2025-08-08 12:00</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2024-06-10 08:00 to 2024-06-24 09:00 (14.04 days) | 2025-05-02 06:00 to 2025-05-12 06:00 (10.00 days)</t>
+          <t>2024-06-10 19:00 to 2024-06-24 20:00 (14.04 days) | 2025-05-02 17:00 to 2025-05-12 17:00 (10.00 days)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2014-12-31 20:00 to 2024-06-10 08:00 | 2024-06-24 09:00 to 2025-05-02 06:00 | 2025-05-12 06:00 to 2025-08-08 01:00</t>
+          <t>2015-01-01 07:00 to 2024-06-10 19:00 | 2024-06-24 20:00 to 2025-05-02 17:00 | 2025-05-12 17:00 to 2025-08-08 12:00</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2012-01-01 10:00</t>
+          <t>2012-01-01 21:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2025-08-07 09:00</t>
+          <t>2025-08-07 20:00</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2024-09-17 21:00 to 2024-10-01 09:00 (13.50 days)</t>
+          <t>2024-09-18 08:00 to 2024-10-01 20:00 (13.50 days)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2012-01-01 10:00 to 2024-09-17 21:00 | 2024-10-01 09:00 to 2025-08-07 09:00</t>
+          <t>2012-01-01 21:00 to 2024-09-18 08:00 | 2024-10-01 20:00 to 2025-08-07 20:00</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2012-01-01 08:00</t>
+          <t>2012-01-01 19:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2023-12-31 01:00</t>
+          <t>2023-12-31 12:00</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -5783,7 +5783,7 @@
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2012-01-01 08:00 to 2023-12-31 01:00</t>
+          <t>2012-01-01 19:00 to 2023-12-31 12:00</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2014-12-31 23:00</t>
+          <t>2015-01-01 10:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2025-08-08 06:00</t>
+          <t>2025-08-08 17:00</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2023-12-25 06:00 to 2024-01-02 17:00 (8.46 days) | 2025-01-01 13:00 to 2025-01-10 04:00 (8.62 days)</t>
+          <t>2023-12-25 17:00 to 2024-01-03 04:00 (8.46 days) | 2025-01-02 00:00 to 2025-01-10 15:00 (8.62 days)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2014-12-31 23:00 to 2023-12-25 06:00 | 2024-01-02 17:00 to 2025-01-01 13:00 | 2025-01-10 04:00 to 2025-08-08 06:00</t>
+          <t>2015-01-01 10:00 to 2023-12-25 17:00 | 2024-01-03 04:00 to 2025-01-02 00:00 | 2025-01-10 15:00 to 2025-08-08 17:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2012-01-01 12:00</t>
+          <t>2012-01-01 23:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2023-12-30 21:00</t>
+          <t>2023-12-31 08:00</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2013-11-01 07:00 to 2013-11-21 02:00 (19.83 days)</t>
+          <t>2013-11-01 18:00 to 2013-11-21 13:00 (19.83 days)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2012-01-01 12:00 to 2013-11-01 07:00 | 2013-11-21 02:00 to 2023-12-30 21:00</t>
+          <t>2012-01-01 23:00 to 2013-11-01 18:00 | 2013-11-21 13:00 to 2023-12-31 08:00</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2014-12-31 18:00</t>
+          <t>2015-01-01 05:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2025-08-08 00:00</t>
+          <t>2025-08-08 11:00</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -5913,7 +5913,7 @@
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2014-12-31 18:00 to 2025-08-08 00:00</t>
+          <t>2015-01-01 05:00 to 2025-08-08 11:00</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2014-12-31 18:00</t>
+          <t>2015-01-01 05:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2025-08-08 04:00</t>
+          <t>2025-08-08 15:00</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -5951,7 +5951,7 @@
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2014-12-31 18:00 to 2025-08-08 04:00</t>
+          <t>2015-01-01 05:00 to 2025-08-08 15:00</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2012-01-01 13:00</t>
+          <t>2012-01-02 00:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2025-08-08 06:00</t>
+          <t>2025-08-08 17:00</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2021-02-10 03:00 to 2021-02-18 15:00 (8.50 days) | 2025-06-26 13:00 to 2025-07-09 17:00 (13.17 days)</t>
+          <t>2021-02-10 14:00 to 2021-02-19 02:00 (8.50 days) | 2025-06-27 00:00 to 2025-07-10 04:00 (13.17 days)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2012-01-01 13:00 to 2021-02-10 03:00 | 2021-02-18 15:00 to 2025-06-26 13:00 | 2025-07-09 17:00 to 2025-08-08 06:00</t>
+          <t>2012-01-02 00:00 to 2021-02-10 14:00 | 2021-02-19 02:00 to 2025-06-27 00:00 | 2025-07-10 04:00 to 2025-08-08 17:00</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2012-06-05 07:00</t>
+          <t>2012-06-05 18:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2023-12-30 23:00</t>
+          <t>2023-12-31 10:00</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -6035,7 +6035,7 @@
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2012-06-05 07:00 to 2023-12-30 23:00</t>
+          <t>2012-06-05 18:00 to 2023-12-31 10:00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2012-06-05 09:00</t>
+          <t>2012-06-05 20:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2025-08-07 19:00</t>
+          <t>2025-08-08 06:00</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -6073,7 +6073,7 @@
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2012-06-05 09:00 to 2025-08-07 19:00</t>
+          <t>2012-06-05 20:00 to 2025-08-08 06:00</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2014-12-31 20:00</t>
+          <t>2015-01-01 07:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2025-08-07 23:00</t>
+          <t>2025-08-08 10:00</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -6111,7 +6111,7 @@
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2014-12-31 20:00 to 2025-08-07 23:00</t>
+          <t>2015-01-01 07:00 to 2025-08-08 10:00</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2012-01-01 12:00</t>
+          <t>2012-01-01 23:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2025-08-07 19:00</t>
+          <t>2025-08-08 06:00</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -6152,12 +6152,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2016-11-30 04:00 to 2016-12-09 04:00 (9.00 days) | 2017-12-23 19:00 to 2018-01-02 15:00 (9.83 days) | 2018-12-03 06:00 to 2019-01-08 07:00 (36.04 days) | 2019-01-13 20:00 to 2019-01-25 09:00 (11.54 days)</t>
+          <t>2016-11-30 15:00 to 2016-12-09 15:00 (9.00 days) | 2017-12-24 06:00 to 2018-01-03 02:00 (9.83 days) | 2018-12-03 17:00 to 2019-01-08 18:00 (36.04 days) | 2019-01-14 07:00 to 2019-01-25 20:00 (11.54 days)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2012-01-01 12:00 to 2016-11-30 04:00 | 2016-12-09 04:00 to 2017-12-23 19:00 | 2018-01-02 15:00 to 2018-12-03 06:00 | 2019-01-08 07:00 to 2019-01-13 20:00 | 2019-01-25 09:00 to 2025-08-07 19:00</t>
+          <t>2012-01-01 23:00 to 2016-11-30 15:00 | 2016-12-09 15:00 to 2017-12-24 06:00 | 2018-01-03 02:00 to 2018-12-03 17:00 | 2019-01-08 18:00 to 2019-01-14 07:00 | 2019-01-25 20:00 to 2025-08-08 06:00</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -6174,12 +6174,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2015-01-01 01:00</t>
+          <t>2015-01-01 12:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2025-08-07 21:00</t>
+          <t>2025-08-08 08:00</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2023-03-07 21:00 to 2023-03-18 10:00 (10.50 days) | 2023-03-22 10:00 to 2023-03-30 22:00 (8.50 days) | 2023-05-31 04:00 to 2023-06-10 03:00 (9.96 days) | 2023-07-20 00:00 to 2023-08-13 14:00 (24.58 days) | 2023-08-13 14:00 to 2023-08-28 09:00 (14.79 days) | 2023-12-28 04:00 to 2024-01-08 05:00 (11.04 days)</t>
+          <t>2023-03-08 08:00 to 2023-03-18 21:00 (10.50 days) | 2023-03-22 21:00 to 2023-03-31 09:00 (8.50 days) | 2023-05-31 15:00 to 2023-06-10 14:00 (9.96 days) | 2023-07-20 11:00 to 2023-08-14 01:00 (24.58 days) | 2023-08-14 01:00 to 2023-08-28 20:00 (14.79 days) | 2023-12-28 15:00 to 2024-01-08 16:00 (11.04 days)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2015-01-01 01:00 to 2023-03-07 21:00 | 2023-03-18 10:00 to 2023-03-22 10:00 | 2023-03-30 22:00 to 2023-05-31 04:00 | 2023-06-10 03:00 to 2023-07-20 00:00 | 2023-08-13 14:00 to 2023-08-13 14:00 | 2023-08-28 09:00 to 2023-12-28 04:00 | 2024-01-08 05:00 to 2025-08-07 21:00</t>
+          <t>2015-01-01 12:00 to 2023-03-08 08:00 | 2023-03-18 21:00 to 2023-03-22 21:00 | 2023-03-31 09:00 to 2023-05-31 15:00 | 2023-06-10 14:00 to 2023-07-20 11:00 | 2023-08-14 01:00 to 2023-08-14 01:00 | 2023-08-28 20:00 to 2023-12-28 15:00 | 2024-01-08 16:00 to 2025-08-08 08:00</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2014-12-31 18:00</t>
+          <t>2015-01-01 05:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2025-08-07 19:00</t>
+          <t>2025-08-08 06:00</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -6241,7 +6241,7 @@
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2014-12-31 18:00 to 2025-08-07 19:00</t>
+          <t>2015-01-01 05:00 to 2025-08-08 06:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2012-01-01 10:00</t>
+          <t>2012-01-01 21:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2025-08-07 23:00</t>
+          <t>2025-08-08 10:00</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -6279,7 +6279,7 @@
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2012-01-01 10:00 to 2025-08-07 23:00</t>
+          <t>2012-01-01 21:00 to 2025-08-08 10:00</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2015-01-01 05:00</t>
+          <t>2015-01-01 16:00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2025-04-10 19:00</t>
+          <t>2025-04-11 06:00</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -6317,7 +6317,7 @@
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2015-01-01 05:00 to 2025-04-10 19:00</t>
+          <t>2015-01-01 16:00 to 2025-04-11 06:00</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2013-01-17 03:00</t>
+          <t>2013-01-17 14:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2025-08-08 00:00</t>
+          <t>2025-08-08 11:00</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2019-12-22 00:00 to 2020-01-29 03:00 (38.12 days) | 2020-01-30 02:00 to 2020-02-12 09:00 (13.29 days) | 2020-02-15 06:00 to 2020-02-23 18:00 (8.50 days) | 2022-02-18 06:00 to 2022-03-06 11:00 (16.21 days) | 2023-12-27 05:00 to 2024-01-07 02:00 (10.88 days) | 2024-01-26 22:00 to 2024-02-04 00:00 (8.08 days) | 2024-05-31 01:00 to 2024-06-07 04:00 (7.12 days) | 2025-02-21 07:00 to 2025-03-04 03:00 (10.83 days) | 2025-04-07 07:00 to 2025-04-14 09:00 (7.08 days)</t>
+          <t>2019-12-22 11:00 to 2020-01-29 14:00 (38.12 days) | 2020-01-30 13:00 to 2020-02-12 20:00 (13.29 days) | 2020-02-15 17:00 to 2020-02-24 05:00 (8.50 days) | 2022-02-18 17:00 to 2022-03-06 22:00 (16.21 days) | 2023-12-27 16:00 to 2024-01-07 13:00 (10.88 days) | 2024-01-27 09:00 to 2024-02-04 11:00 (8.08 days) | 2024-05-31 12:00 to 2024-06-07 15:00 (7.12 days) | 2025-02-21 18:00 to 2025-03-04 14:00 (10.83 days) | 2025-04-07 18:00 to 2025-04-14 20:00 (7.08 days)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2013-01-17 03:00 to 2019-12-22 00:00 | 2020-01-29 03:00 to 2020-01-30 02:00 | 2020-02-12 09:00 to 2020-02-15 06:00 | 2020-02-23 18:00 to 2022-02-18 06:00 | 2022-03-06 11:00 to 2023-12-27 05:00 | 2024-01-07 02:00 to 2024-01-26 22:00 | 2024-02-04 00:00 to 2024-05-31 01:00 | 2024-06-07 04:00 to 2025-02-21 07:00 | 2025-03-04 03:00 to 2025-04-07 07:00 | 2025-04-14 09:00 to 2025-08-08 00:00</t>
+          <t>2013-01-17 14:00 to 2019-12-22 11:00 | 2020-01-29 14:00 to 2020-01-30 13:00 | 2020-02-12 20:00 to 2020-02-15 17:00 | 2020-02-24 05:00 to 2022-02-18 17:00 | 2022-03-06 22:00 to 2023-12-27 16:00 | 2024-01-07 13:00 to 2024-01-27 09:00 | 2024-02-04 11:00 to 2024-05-31 12:00 | 2024-06-07 15:00 to 2025-02-21 18:00 | 2025-03-04 14:00 to 2025-04-07 18:00 | 2025-04-14 20:00 to 2025-08-08 11:00</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2014-12-31 22:00</t>
+          <t>2015-01-01 09:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2023-12-31 02:00</t>
+          <t>2023-12-31 13:00</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -6401,7 +6401,7 @@
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2014-12-31 22:00 to 2023-12-31 02:00</t>
+          <t>2015-01-01 09:00 to 2023-12-31 13:00</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2020-10-09 16:00</t>
+          <t>2020-10-10 03:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2025-08-08 05:00</t>
+          <t>2025-08-08 16:00</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2025-01-05 17:00 to 2025-03-13 10:00 (66.67 days)</t>
+          <t>2025-01-06 04:00 to 2025-03-13 21:00 (66.67 days)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2020-10-09 16:00 to 2025-01-05 17:00 | 2025-03-13 10:00 to 2025-08-08 05:00</t>
+          <t>2020-10-10 03:00 to 2025-01-06 04:00 | 2025-03-13 21:00 to 2025-08-08 16:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2014-12-31 22:00</t>
+          <t>2015-01-01 09:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2025-08-08 01:00</t>
+          <t>2025-08-08 12:00</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -6485,7 +6485,7 @@
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2014-12-31 22:00 to 2025-08-08 01:00</t>
+          <t>2015-01-01 09:00 to 2025-08-08 12:00</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -6502,12 +6502,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2015-01-01 00:00</t>
+          <t>2015-01-01 11:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2025-08-08 04:00</t>
+          <t>2025-08-08 15:00</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -6523,7 +6523,7 @@
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2015-01-01 00:00 to 2025-08-08 04:00</t>
+          <t>2015-01-01 11:00 to 2025-08-08 15:00</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2015-01-01 02:00</t>
+          <t>2015-01-01 13:00</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2025-08-07 22:00</t>
+          <t>2025-08-08 09:00</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2021-08-11 10:00 to 2022-10-07 07:00 (421.88 days) | 2023-12-24 08:00 to 2024-01-02 03:00 (8.79 days) | 2024-09-18 16:00 to 2024-10-07 04:00 (18.50 days) | 2025-01-04 16:00 to 2025-01-14 10:00 (9.75 days)</t>
+          <t>2021-08-11 21:00 to 2022-10-07 18:00 (421.88 days) | 2023-12-24 19:00 to 2024-01-02 14:00 (8.79 days) | 2024-09-19 03:00 to 2024-10-07 15:00 (18.50 days) | 2025-01-05 03:00 to 2025-01-14 21:00 (9.75 days)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2015-01-01 02:00 to 2021-08-11 10:00 | 2022-10-07 07:00 to 2023-12-24 08:00 | 2024-01-02 03:00 to 2024-09-18 16:00 | 2024-10-07 04:00 to 2025-01-04 16:00 | 2025-01-14 10:00 to 2025-08-07 22:00</t>
+          <t>2015-01-01 13:00 to 2021-08-11 21:00 | 2022-10-07 18:00 to 2023-12-24 19:00 | 2024-01-02 14:00 to 2024-09-19 03:00 | 2024-10-07 15:00 to 2025-01-05 03:00 | 2025-01-14 21:00 to 2025-08-08 09:00</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2013-08-09 16:00</t>
+          <t>2013-08-10 03:00</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2025-08-07 19:00</t>
+          <t>2025-08-08 06:00</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -6607,7 +6607,7 @@
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2013-08-09 16:00 to 2025-08-07 19:00</t>
+          <t>2013-08-10 03:00 to 2025-08-08 06:00</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2012-01-01 09:00</t>
+          <t>2012-01-01 20:00</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2025-08-08 04:00</t>
+          <t>2025-08-08 15:00</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -6645,7 +6645,7 @@
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2012-01-01 09:00 to 2025-08-08 04:00</t>
+          <t>2012-01-01 20:00 to 2025-08-08 15:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2012-01-01 11:00</t>
+          <t>2012-01-01 22:00</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2025-08-07 22:00</t>
+          <t>2025-08-08 09:00</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -6683,7 +6683,7 @@
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2012-01-01 11:00 to 2025-08-07 22:00</t>
+          <t>2012-01-01 22:00 to 2025-08-08 09:00</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2012-01-01 09:00</t>
+          <t>2012-01-01 20:00</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2025-08-08 05:00</t>
+          <t>2025-08-08 16:00</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2021-06-17 18:00 to 2021-06-29 06:00 (11.50 days) | 2025-02-11 03:00 to 2025-02-20 01:00 (8.92 days)</t>
+          <t>2021-06-18 05:00 to 2021-06-29 17:00 (11.50 days) | 2025-02-11 14:00 to 2025-02-20 12:00 (8.92 days)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2012-01-01 09:00 to 2021-06-17 18:00 | 2021-06-29 06:00 to 2025-02-11 03:00 | 2025-02-20 01:00 to 2025-08-08 05:00</t>
+          <t>2012-01-01 20:00 to 2021-06-18 05:00 | 2021-06-29 17:00 to 2025-02-11 14:00 | 2025-02-20 12:00 to 2025-08-08 16:00</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2012-01-01 08:00</t>
+          <t>2012-01-01 19:00</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2025-08-08 00:00</t>
+          <t>2025-08-08 11:00</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -6767,7 +6767,7 @@
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2012-01-01 08:00 to 2025-08-08 00:00</t>
+          <t>2012-01-01 19:00 to 2025-08-08 11:00</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2012-01-01 12:00</t>
+          <t>2012-01-01 23:00</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2025-08-07 19:00</t>
+          <t>2025-08-08 06:00</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -6805,7 +6805,7 @@
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2012-01-01 12:00 to 2025-08-07 19:00</t>
+          <t>2012-01-01 23:00 to 2025-08-08 06:00</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2012-01-01 09:00</t>
+          <t>2012-01-01 20:00</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2025-07-31 06:00</t>
+          <t>2025-07-31 17:00</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2023-12-25 16:00 to 2024-01-02 04:00 (7.50 days)</t>
+          <t>2023-12-26 03:00 to 2024-01-02 15:00 (7.50 days)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2012-01-01 09:00 to 2023-12-25 16:00 | 2024-01-02 04:00 to 2025-07-31 06:00</t>
+          <t>2012-01-01 20:00 to 2023-12-26 03:00 | 2024-01-02 15:00 to 2025-07-31 17:00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2012-01-02 08:00</t>
+          <t>2012-01-02 19:00</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2025-08-08 06:00</t>
+          <t>2025-08-08 17:00</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2018-09-05 05:00 to 2018-09-20 22:00 (15.71 days) | 2018-09-20 23:00 to 2018-09-28 07:00 (7.33 days) | 2024-09-17 14:00 to 2024-10-01 00:00 (13.42 days) | 2025-05-23 01:00 to 2025-06-03 16:00 (11.62 days)</t>
+          <t>2018-09-05 16:00 to 2018-09-21 09:00 (15.71 days) | 2018-09-21 10:00 to 2018-09-28 18:00 (7.33 days) | 2024-09-18 01:00 to 2024-10-01 11:00 (13.42 days) | 2025-05-23 12:00 to 2025-06-04 03:00 (11.62 days)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2012-01-02 08:00 to 2018-09-05 05:00 | 2018-09-20 22:00 to 2018-09-20 23:00 | 2018-09-28 07:00 to 2024-09-17 14:00 | 2024-10-01 00:00 to 2025-05-23 01:00 | 2025-06-03 16:00 to 2025-08-08 06:00</t>
+          <t>2012-01-02 19:00 to 2018-09-05 16:00 | 2018-09-21 09:00 to 2018-09-21 10:00 | 2018-09-28 18:00 to 2024-09-18 01:00 | 2024-10-01 11:00 to 2025-05-23 12:00 | 2025-06-04 03:00 to 2025-08-08 17:00</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2012-01-01 08:00</t>
+          <t>2012-01-01 19:00</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2025-08-08 00:00</t>
+          <t>2025-08-08 11:00</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -6935,7 +6935,7 @@
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2012-01-01 08:00 to 2025-08-08 00:00</t>
+          <t>2012-01-01 19:00 to 2025-08-08 11:00</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2012-01-01 11:00</t>
+          <t>2012-01-01 22:00</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2025-08-07 21:00</t>
+          <t>2025-08-08 08:00</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -6976,12 +6976,12 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2017-12-25 06:00 to 2018-01-02 04:00 (7.92 days) | 2021-02-08 17:00 to 2021-02-16 05:00 (7.50 days)</t>
+          <t>2017-12-25 17:00 to 2018-01-02 15:00 (7.92 days) | 2021-02-09 04:00 to 2021-02-16 16:00 (7.50 days)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2012-01-01 11:00 to 2017-12-25 06:00 | 2018-01-02 04:00 to 2021-02-08 17:00 | 2021-02-16 05:00 to 2025-08-07 21:00</t>
+          <t>2012-01-01 22:00 to 2017-12-25 17:00 | 2018-01-02 15:00 to 2021-02-09 04:00 | 2021-02-16 16:00 to 2025-08-08 08:00</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2012-01-01 19:00</t>
+          <t>2012-01-02 06:00</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2025-08-07 19:00</t>
+          <t>2025-08-08 06:00</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -7019,7 +7019,7 @@
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2012-01-01 19:00 to 2025-08-07 19:00</t>
+          <t>2012-01-02 06:00 to 2025-08-08 06:00</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -7036,12 +7036,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2012-01-01 09:00</t>
+          <t>2012-01-01 20:00</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2025-08-08 06:00</t>
+          <t>2025-08-08 17:00</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2017-09-24 21:00 to 2017-12-09 10:00 (75.58 days)</t>
+          <t>2017-09-25 08:00 to 2017-12-09 21:00 (75.58 days)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2012-01-01 09:00 to 2017-09-24 21:00 | 2017-12-09 10:00 to 2025-08-08 06:00</t>
+          <t>2012-01-01 20:00 to 2017-09-25 08:00 | 2017-12-09 21:00 to 2025-08-08 17:00</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2012-01-01 19:00</t>
+          <t>2012-01-02 06:00</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2025-08-08 04:00</t>
+          <t>2025-08-08 15:00</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -7103,7 +7103,7 @@
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2012-01-01 19:00 to 2025-08-08 04:00</t>
+          <t>2012-01-02 06:00 to 2025-08-08 15:00</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00</t>
+          <t>2012-01-02 04:00</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2025-08-08 04:00</t>
+          <t>2025-08-08 15:00</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -7141,7 +7141,7 @@
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2012-01-01 17:00 to 2025-08-08 04:00</t>
+          <t>2012-01-02 04:00 to 2025-08-08 15:00</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2012-01-01 10:00</t>
+          <t>2012-01-01 21:00</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2025-08-07 23:00</t>
+          <t>2025-08-08 10:00</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2022-07-15 04:00 to 2022-09-22 06:00 (69.08 days)</t>
+          <t>2022-07-15 15:00 to 2022-09-22 17:00 (69.08 days)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2012-01-01 10:00 to 2022-07-15 04:00 | 2022-09-22 06:00 to 2025-08-07 23:00</t>
+          <t>2012-01-01 21:00 to 2022-07-15 15:00 | 2022-09-22 17:00 to 2025-08-08 10:00</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -7204,12 +7204,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2013-06-27 15:00</t>
+          <t>2013-06-28 02:00</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2025-08-07 19:00</t>
+          <t>2025-08-08 06:00</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -7228,12 +7228,12 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2016-04-27 06:00 to 2016-05-09 17:00 (12.46 days) | 2024-02-05 19:00 to 2024-02-28 18:00 (22.96 days) | 2024-02-28 18:00 to 2024-03-11 11:00 (11.67 days) | 2024-03-11 11:00 to 2024-08-28 04:00 (169.71 days) | 2024-08-28 04:00 to 2025-06-16 03:00 (291.96 days)</t>
+          <t>2016-04-27 17:00 to 2016-05-10 04:00 (12.46 days) | 2024-02-06 06:00 to 2024-02-29 05:00 (22.96 days) | 2024-02-29 05:00 to 2024-03-11 22:00 (11.67 days) | 2024-03-11 22:00 to 2024-08-28 15:00 (169.71 days) | 2024-08-28 15:00 to 2025-06-16 14:00 (291.96 days)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2013-06-27 15:00 to 2016-04-27 06:00 | 2016-05-09 17:00 to 2024-02-05 19:00 | 2024-02-28 18:00 to 2024-02-28 18:00 | 2024-03-11 11:00 to 2024-03-11 11:00 | 2024-08-28 04:00 to 2024-08-28 04:00 | 2025-06-16 03:00 to 2025-08-07 19:00</t>
+          <t>2013-06-28 02:00 to 2016-04-27 17:00 | 2016-05-10 04:00 to 2024-02-06 06:00 | 2024-02-29 05:00 to 2024-02-29 05:00 | 2024-03-11 22:00 to 2024-03-11 22:00 | 2024-08-28 15:00 to 2024-08-28 15:00 | 2025-06-16 14:00 to 2025-08-08 06:00</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2012-05-24 14:00</t>
+          <t>2012-05-25 01:00</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2023-12-24 15:00</t>
+          <t>2023-12-25 02:00</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2017-01-03 10:00 to 2021-09-23 03:00 (1723.67 days) | 2022-01-11 17:00 to 2022-04-28 09:00 (106.62 days) | 2022-04-28 09:00 to 2022-05-10 20:00 (12.46 days) | 2022-05-15 03:00 to 2022-05-30 22:00 (15.79 days) | 2022-05-30 22:00 to 2022-06-10 15:00 (10.71 days) | 2022-06-10 15:00 to 2022-07-07 01:00 (26.42 days) | 2022-11-13 17:00 to 2023-01-27 06:00 (74.54 days) | 2023-01-27 06:00 to 2023-02-11 02:00 (14.83 days) | 2023-02-11 02:00 to 2023-05-07 11:00 (85.33 days) | 2023-10-27 03:00 to 2023-11-04 10:00 (8.29 days) | 2023-11-18 11:00 to 2023-11-26 07:00 (7.83 days) | 2023-11-29 10:00 to 2023-12-07 09:00 (7.96 days) | 2023-12-13 09:00 to 2023-12-23 21:00 (10.50 days)</t>
+          <t>2017-01-03 21:00 to 2021-09-23 14:00 (1723.67 days) | 2022-01-12 04:00 to 2022-04-28 20:00 (106.62 days) | 2022-04-28 20:00 to 2022-05-11 07:00 (12.46 days) | 2022-05-15 14:00 to 2022-05-31 09:00 (15.79 days) | 2022-05-31 09:00 to 2022-06-11 02:00 (10.71 days) | 2022-06-11 02:00 to 2022-07-07 12:00 (26.42 days) | 2022-11-14 04:00 to 2023-01-27 17:00 (74.54 days) | 2023-01-27 17:00 to 2023-02-11 13:00 (14.83 days) | 2023-02-11 13:00 to 2023-05-07 22:00 (85.33 days) | 2023-10-27 14:00 to 2023-11-04 21:00 (8.29 days) | 2023-11-18 22:00 to 2023-11-26 18:00 (7.83 days) | 2023-11-29 21:00 to 2023-12-07 20:00 (7.96 days) | 2023-12-13 20:00 to 2023-12-24 08:00 (10.50 days)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2012-05-24 14:00 to 2017-01-03 10:00 | 2021-09-23 03:00 to 2022-01-11 17:00 | 2022-04-28 09:00 to 2022-04-28 09:00 | 2022-05-10 20:00 to 2022-05-15 03:00 | 2022-05-30 22:00 to 2022-05-30 22:00 | 2022-06-10 15:00 to 2022-06-10 15:00 | 2022-07-07 01:00 to 2022-11-13 17:00 | 2023-01-27 06:00 to 2023-01-27 06:00 | 2023-02-11 02:00 to 2023-02-11 02:00 | 2023-05-07 11:00 to 2023-10-27 03:00 | 2023-11-04 10:00 to 2023-11-18 11:00 | 2023-11-26 07:00 to 2023-11-29 10:00 | 2023-12-07 09:00 to 2023-12-13 09:00 | 2023-12-23 21:00 to 2023-12-24 15:00</t>
+          <t>2012-05-25 01:00 to 2017-01-03 21:00 | 2021-09-23 14:00 to 2022-01-12 04:00 | 2022-04-28 20:00 to 2022-04-28 20:00 | 2022-05-11 07:00 to 2022-05-15 14:00 | 2022-05-31 09:00 to 2022-05-31 09:00 | 2022-06-11 02:00 to 2022-06-11 02:00 | 2022-07-07 12:00 to 2022-11-14 04:00 | 2023-01-27 17:00 to 2023-01-27 17:00 | 2023-02-11 13:00 to 2023-02-11 13:00 | 2023-05-07 22:00 to 2023-10-27 14:00 | 2023-11-04 21:00 to 2023-11-18 22:00 | 2023-11-26 18:00 to 2023-11-29 21:00 | 2023-12-07 20:00 to 2023-12-13 20:00 | 2023-12-24 08:00 to 2023-12-25 02:00</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2012-05-24 14:00</t>
+          <t>2012-05-25 01:00</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2023-04-19 11:00</t>
+          <t>2023-04-19 22:00</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -7320,12 +7320,12 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2016-12-07 07:00 to 2022-08-16 05:00 (2077.88 days) | 2022-12-14 17:00 to 2023-01-27 07:00 (43.58 days)</t>
+          <t>2016-12-07 18:00 to 2022-08-16 16:00 (2077.88 days) | 2022-12-15 04:00 to 2023-01-27 18:00 (43.58 days)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2012-05-24 14:00 to 2016-12-07 07:00 | 2022-08-16 05:00 to 2022-12-14 17:00 | 2023-01-27 07:00 to 2023-04-19 11:00</t>
+          <t>2012-05-25 01:00 to 2016-12-07 18:00 | 2022-08-16 16:00 to 2022-12-15 04:00 | 2023-01-27 18:00 to 2023-04-19 22:00</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2012-05-21 01:00</t>
+          <t>2012-05-21 12:00</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2017-06-17 18:00</t>
+          <t>2017-06-18 05:00</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -7363,7 +7363,7 @@
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2012-05-21 01:00 to 2017-06-17 18:00</t>
+          <t>2012-05-21 12:00 to 2017-06-18 05:00</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2013-06-28 22:00</t>
+          <t>2013-06-29 09:00</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2023-12-30 18:00</t>
+          <t>2023-12-31 05:00</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -7401,7 +7401,7 @@
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2013-06-28 22:00 to 2023-12-30 18:00</t>
+          <t>2013-06-29 09:00 to 2023-12-31 05:00</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2013-06-29 03:00</t>
+          <t>2013-06-29 14:00</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2025-08-07 22:00</t>
+          <t>2025-08-08 09:00</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -7442,12 +7442,12 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2022-08-19 18:00 to 2025-06-23 22:00 (1039.17 days)</t>
+          <t>2022-08-20 05:00 to 2025-06-24 09:00 (1039.17 days)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2013-06-29 03:00 to 2022-08-19 18:00 | 2025-06-23 22:00 to 2025-08-07 22:00</t>
+          <t>2013-06-29 14:00 to 2022-08-20 05:00 | 2025-06-24 09:00 to 2025-08-08 09:00</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2013-06-27 17:00</t>
+          <t>2013-06-28 04:00</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2015-05-29 02:00</t>
+          <t>2015-05-29 13:00</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2015-04-29 22:00 to 2015-05-07 15:00 (7.71 days) | 2015-05-21 23:00 to 2015-05-29 02:00 (7.12 days)</t>
+          <t>2015-04-30 09:00 to 2015-05-08 02:00 (7.71 days) | 2015-05-22 10:00 to 2015-05-29 13:00 (7.12 days)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>2013-06-27 17:00 to 2015-04-29 22:00 | 2015-05-07 15:00 to 2015-05-21 23:00 | 2015-05-29 02:00 to 2015-05-29 02:00</t>
+          <t>2013-06-28 04:00 to 2015-04-30 09:00 | 2015-05-08 02:00 to 2015-05-22 10:00 | 2015-05-29 13:00 to 2015-05-29 13:00</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2013-06-27 14:00</t>
+          <t>2013-06-28 01:00</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2023-12-30 19:00</t>
+          <t>2023-12-31 06:00</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2013-09-01 04:00 to 2013-09-10 03:00 (8.96 days) | 2014-04-27 14:00 to 2014-05-08 03:00 (10.54 days) | 2014-05-26 18:00 to 2014-06-12 05:00 (16.46 days) | 2014-07-08 04:00 to 2014-07-15 16:00 (7.50 days) | 2015-09-18 02:00 to 2015-12-29 04:00 (102.12 days) | 2017-05-18 15:00 to 2017-06-16 19:00 (29.17 days) | 2017-07-13 03:00 to 2021-07-28 12:00 (1476.38 days)</t>
+          <t>2013-09-01 15:00 to 2013-09-10 14:00 (8.96 days) | 2014-04-28 01:00 to 2014-05-08 14:00 (10.54 days) | 2014-05-27 05:00 to 2014-06-12 16:00 (16.46 days) | 2014-07-08 15:00 to 2014-07-16 03:00 (7.50 days) | 2015-09-18 13:00 to 2015-12-29 15:00 (102.12 days) | 2017-05-19 02:00 to 2017-06-17 06:00 (29.17 days) | 2017-07-13 14:00 to 2021-07-28 23:00 (1476.38 days)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2013-06-27 14:00 to 2013-09-01 04:00 | 2013-09-10 03:00 to 2014-04-27 14:00 | 2014-05-08 03:00 to 2014-05-26 18:00 | 2014-06-12 05:00 to 2014-07-08 04:00 | 2014-07-15 16:00 to 2015-09-18 02:00 | 2015-12-29 04:00 to 2017-05-18 15:00 | 2017-06-16 19:00 to 2017-07-13 03:00 | 2021-07-28 12:00 to 2023-12-30 19:00</t>
+          <t>2013-06-28 01:00 to 2013-09-01 15:00 | 2013-09-10 14:00 to 2014-04-28 01:00 | 2014-05-08 14:00 to 2014-05-27 05:00 | 2014-06-12 16:00 to 2014-07-08 15:00 | 2014-07-16 03:00 to 2015-09-18 13:00 | 2015-12-29 15:00 to 2017-05-19 02:00 | 2017-06-17 06:00 to 2017-07-13 14:00 | 2021-07-28 23:00 to 2023-12-31 06:00</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
